--- a/research/traditional_assets/database/data/egypt/egypt_healthcare_support_services.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_healthcare_support_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.163984257366324</v>
+        <v>0.1636501677872498</v>
       </c>
       <c r="C2">
-        <v>571.8942798900084</v>
+        <v>568.5466617674317</v>
       </c>
       <c r="D2">
-        <v>552.8942798900084</v>
+        <v>554.4616617674317</v>
       </c>
       <c r="E2">
-        <v>-352.7</v>
+        <v>-347.785</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.915</v>
       </c>
       <c r="G2">
         <v>19</v>
@@ -1451,28 +1451,28 @@
         <v>64.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2472245</v>
       </c>
       <c r="N2">
-        <v>64.8</v>
+        <v>64.5527755</v>
       </c>
       <c r="O2">
-        <v>14.58</v>
+        <v>14.5243744875</v>
       </c>
       <c r="P2">
-        <v>50.22</v>
+        <v>50.0284010125</v>
       </c>
       <c r="Q2">
-        <v>52.92</v>
+        <v>52.7284010125</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.163984257366324</v>
+        <v>0.1649094371588382</v>
       </c>
       <c r="T2">
-        <v>0.8240329453738457</v>
+        <v>0.830483708330055</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>262.1099446050048</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1636501677872498</v>
+        <v>0.1633160782081756</v>
       </c>
       <c r="C3">
-        <v>568.5466617674317</v>
+        <v>565.2079555479688</v>
       </c>
       <c r="D3">
-        <v>554.4616617674317</v>
+        <v>556.0379555479689</v>
       </c>
       <c r="E3">
-        <v>-347.785</v>
+        <v>-342.87</v>
       </c>
       <c r="F3">
-        <v>4.915</v>
+        <v>9.83</v>
       </c>
       <c r="G3">
         <v>19</v>
@@ -1533,28 +1533,28 @@
         <v>64.8</v>
       </c>
       <c r="M3">
-        <v>0.2472245</v>
+        <v>0.494449</v>
       </c>
       <c r="N3">
-        <v>64.5527755</v>
+        <v>64.30555099999999</v>
       </c>
       <c r="O3">
-        <v>14.5243744875</v>
+        <v>14.468748975</v>
       </c>
       <c r="P3">
-        <v>50.0284010125</v>
+        <v>49.836802025</v>
       </c>
       <c r="Q3">
-        <v>52.7284010125</v>
+        <v>52.536802025</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1649094371588382</v>
+        <v>0.1658534981716077</v>
       </c>
       <c r="T3">
-        <v>0.830483708330055</v>
+        <v>0.8370661195098605</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>262.1099446050048</v>
+        <v>131.0549723025024</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1633160782081756</v>
+        <v>0.1629819886291014</v>
       </c>
       <c r="C4">
-        <v>565.2079555479688</v>
+        <v>561.8782374559785</v>
       </c>
       <c r="D4">
-        <v>556.0379555479689</v>
+        <v>557.6232374559785</v>
       </c>
       <c r="E4">
-        <v>-342.87</v>
+        <v>-337.955</v>
       </c>
       <c r="F4">
-        <v>9.83</v>
+        <v>14.745</v>
       </c>
       <c r="G4">
         <v>19</v>
@@ -1615,28 +1615,28 @@
         <v>64.8</v>
       </c>
       <c r="M4">
-        <v>0.494449</v>
+        <v>0.7416734999999999</v>
       </c>
       <c r="N4">
-        <v>64.30555099999999</v>
+        <v>64.05832649999999</v>
       </c>
       <c r="O4">
-        <v>14.468748975</v>
+        <v>14.4131234625</v>
       </c>
       <c r="P4">
-        <v>49.836802025</v>
+        <v>49.6452030375</v>
       </c>
       <c r="Q4">
-        <v>52.536802025</v>
+        <v>52.3452030375</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1658534981716077</v>
+        <v>0.1668170243598983</v>
       </c>
       <c r="T4">
-        <v>0.8370661195098605</v>
+        <v>0.8437842505078064</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>131.0549723025024</v>
+        <v>87.36998153500159</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1629819886291014</v>
+        <v>0.1626478990500271</v>
       </c>
       <c r="C5">
-        <v>561.8782374559785</v>
+        <v>558.5575845875767</v>
       </c>
       <c r="D5">
-        <v>557.6232374559785</v>
+        <v>559.2175845875767</v>
       </c>
       <c r="E5">
-        <v>-337.955</v>
+        <v>-333.04</v>
       </c>
       <c r="F5">
-        <v>14.745</v>
+        <v>19.66</v>
       </c>
       <c r="G5">
         <v>19</v>
@@ -1697,28 +1697,28 @@
         <v>64.8</v>
       </c>
       <c r="M5">
-        <v>0.7416734999999999</v>
+        <v>0.9888979999999999</v>
       </c>
       <c r="N5">
-        <v>64.05832649999999</v>
+        <v>63.811102</v>
       </c>
       <c r="O5">
-        <v>14.4131234625</v>
+        <v>14.35749795</v>
       </c>
       <c r="P5">
-        <v>49.6452030375</v>
+        <v>49.45360405</v>
       </c>
       <c r="Q5">
-        <v>52.3452030375</v>
+        <v>52.15360405</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1668170243598983</v>
+        <v>0.1678006240104449</v>
       </c>
       <c r="T5">
-        <v>0.8437842505078064</v>
+        <v>0.8506423425682095</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>87.36998153500159</v>
+        <v>65.5274861512512</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1626478990500271</v>
+        <v>0.1623138094709529</v>
       </c>
       <c r="C6">
-        <v>558.5575845875767</v>
+        <v>555.2460749231351</v>
       </c>
       <c r="D6">
-        <v>559.2175845875767</v>
+        <v>560.8210749231351</v>
       </c>
       <c r="E6">
-        <v>-333.04</v>
+        <v>-328.125</v>
       </c>
       <c r="F6">
-        <v>19.66</v>
+        <v>24.575</v>
       </c>
       <c r="G6">
         <v>19</v>
@@ -1779,28 +1779,28 @@
         <v>64.8</v>
       </c>
       <c r="M6">
-        <v>0.9888979999999999</v>
+        <v>1.2361225</v>
       </c>
       <c r="N6">
-        <v>63.811102</v>
+        <v>63.5638775</v>
       </c>
       <c r="O6">
-        <v>14.35749795</v>
+        <v>14.3018724375</v>
       </c>
       <c r="P6">
-        <v>49.45360405</v>
+        <v>49.26200506249999</v>
       </c>
       <c r="Q6">
-        <v>52.15360405</v>
+        <v>51.9620050625</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1678006240104449</v>
+        <v>0.1688049310220557</v>
       </c>
       <c r="T6">
-        <v>0.8506423425682095</v>
+        <v>0.8576448155140947</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>65.5274861512512</v>
+        <v>52.42198892100095</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1623138094709529</v>
+        <v>0.1619797198918787</v>
       </c>
       <c r="C7">
-        <v>555.2460749231351</v>
+        <v>551.9437873399958</v>
       </c>
       <c r="D7">
-        <v>560.8210749231351</v>
+        <v>562.4337873399958</v>
       </c>
       <c r="E7">
-        <v>-328.125</v>
+        <v>-323.21</v>
       </c>
       <c r="F7">
-        <v>24.575</v>
+        <v>29.49</v>
       </c>
       <c r="G7">
         <v>19</v>
@@ -1861,28 +1861,28 @@
         <v>64.8</v>
       </c>
       <c r="M7">
-        <v>1.2361225</v>
+        <v>1.483347</v>
       </c>
       <c r="N7">
-        <v>63.5638775</v>
+        <v>63.316653</v>
       </c>
       <c r="O7">
-        <v>14.3018724375</v>
+        <v>14.246246925</v>
       </c>
       <c r="P7">
-        <v>49.26200506249999</v>
+        <v>49.07040607499999</v>
       </c>
       <c r="Q7">
-        <v>51.9620050625</v>
+        <v>51.770406075</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1688049310220557</v>
+        <v>0.169830606267956</v>
       </c>
       <c r="T7">
-        <v>0.8576448155140947</v>
+        <v>0.8647962772460626</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>52.42198892100095</v>
+        <v>43.68499076750079</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1619797198918787</v>
+        <v>0.1616456303128045</v>
       </c>
       <c r="C8">
-        <v>551.9437873399958</v>
+        <v>548.6508016254045</v>
       </c>
       <c r="D8">
-        <v>562.4337873399958</v>
+        <v>564.0558016254045</v>
       </c>
       <c r="E8">
-        <v>-323.21</v>
+        <v>-318.295</v>
       </c>
       <c r="F8">
-        <v>29.49</v>
+        <v>34.40499999999999</v>
       </c>
       <c r="G8">
         <v>19</v>
@@ -1943,28 +1943,28 @@
         <v>64.8</v>
       </c>
       <c r="M8">
-        <v>1.483347</v>
+        <v>1.7305715</v>
       </c>
       <c r="N8">
-        <v>63.316653</v>
+        <v>63.0694285</v>
       </c>
       <c r="O8">
-        <v>14.246246925</v>
+        <v>14.1906214125</v>
       </c>
       <c r="P8">
-        <v>49.07040607499999</v>
+        <v>48.8788070875</v>
       </c>
       <c r="Q8">
-        <v>51.770406075</v>
+        <v>51.5788070875</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.169830606267956</v>
+        <v>0.1708783390460263</v>
       </c>
       <c r="T8">
-        <v>0.8647962772460626</v>
+        <v>0.8721015338539868</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>43.6849907675008</v>
+        <v>37.44427780071497</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1616456303128045</v>
+        <v>0.1613115407337302</v>
       </c>
       <c r="C9">
-        <v>548.6508016254045</v>
+        <v>545.3671984896692</v>
       </c>
       <c r="D9">
-        <v>564.0558016254045</v>
+        <v>565.6871984896693</v>
       </c>
       <c r="E9">
-        <v>-318.295</v>
+        <v>-313.38</v>
       </c>
       <c r="F9">
-        <v>34.405</v>
+        <v>39.32</v>
       </c>
       <c r="G9">
         <v>19</v>
@@ -2025,28 +2025,28 @@
         <v>64.8</v>
       </c>
       <c r="M9">
-        <v>1.7305715</v>
+        <v>1.977796</v>
       </c>
       <c r="N9">
-        <v>63.0694285</v>
+        <v>62.822204</v>
       </c>
       <c r="O9">
-        <v>14.1906214125</v>
+        <v>14.1349959</v>
       </c>
       <c r="P9">
-        <v>48.8788070875</v>
+        <v>48.6872081</v>
       </c>
       <c r="Q9">
-        <v>51.5788070875</v>
+        <v>51.3872081</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1708783390460263</v>
+        <v>0.1719488486236198</v>
       </c>
       <c r="T9">
-        <v>0.8721015338539868</v>
+        <v>0.8795656003881701</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>37.44427780071497</v>
+        <v>32.7637430756256</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1613115407337302</v>
+        <v>0.160977451154656</v>
       </c>
       <c r="C10">
-        <v>545.3671984896692</v>
+        <v>542.0930595795481</v>
       </c>
       <c r="D10">
-        <v>565.6871984896693</v>
+        <v>567.3280595795482</v>
       </c>
       <c r="E10">
-        <v>-313.38</v>
+        <v>-308.465</v>
       </c>
       <c r="F10">
-        <v>39.32</v>
+        <v>44.235</v>
       </c>
       <c r="G10">
         <v>19</v>
@@ -2107,28 +2107,28 @@
         <v>64.8</v>
       </c>
       <c r="M10">
-        <v>1.977796</v>
+        <v>2.2250205</v>
       </c>
       <c r="N10">
-        <v>62.822204</v>
+        <v>62.5749795</v>
       </c>
       <c r="O10">
-        <v>14.1349959</v>
+        <v>14.0793703875</v>
       </c>
       <c r="P10">
-        <v>48.6872081</v>
+        <v>48.4956091125</v>
       </c>
       <c r="Q10">
-        <v>51.3872081</v>
+        <v>51.1956091125</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1719488486236198</v>
+        <v>0.1730428858842374</v>
       </c>
       <c r="T10">
-        <v>0.8795656003881701</v>
+        <v>0.8871937123406872</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>32.7637430756256</v>
+        <v>29.12332717833386</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.160977451154656</v>
+        <v>0.1606433615755818</v>
       </c>
       <c r="C11">
-        <v>542.0930595795481</v>
+        <v>538.8284674918696</v>
       </c>
       <c r="D11">
-        <v>567.3280595795482</v>
+        <v>568.9784674918695</v>
       </c>
       <c r="E11">
-        <v>-308.465</v>
+        <v>-303.55</v>
       </c>
       <c r="F11">
-        <v>44.235</v>
+        <v>49.15</v>
       </c>
       <c r="G11">
         <v>19</v>
@@ -2189,28 +2189,28 @@
         <v>64.8</v>
       </c>
       <c r="M11">
-        <v>2.2250205</v>
+        <v>2.472245</v>
       </c>
       <c r="N11">
-        <v>62.5749795</v>
+        <v>62.327755</v>
       </c>
       <c r="O11">
-        <v>14.0793703875</v>
+        <v>14.023744875</v>
       </c>
       <c r="P11">
-        <v>48.4956091125</v>
+        <v>48.304010125</v>
       </c>
       <c r="Q11">
-        <v>51.1956091125</v>
+        <v>51.004010125</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1730428858842374</v>
+        <v>0.1741612350839797</v>
       </c>
       <c r="T11">
-        <v>0.8871937123406872</v>
+        <v>0.894991337892149</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>29.12332717833386</v>
+        <v>26.21099446050047</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1606433615755818</v>
+        <v>0.1603092719965075</v>
       </c>
       <c r="C12">
-        <v>538.8284674918696</v>
+        <v>535.5735057873924</v>
       </c>
       <c r="D12">
-        <v>568.9784674918695</v>
+        <v>570.6385057873924</v>
       </c>
       <c r="E12">
-        <v>-303.55</v>
+        <v>-298.635</v>
       </c>
       <c r="F12">
-        <v>49.15000000000001</v>
+        <v>54.065</v>
       </c>
       <c r="G12">
         <v>19</v>
@@ -2271,28 +2271,28 @@
         <v>64.8</v>
       </c>
       <c r="M12">
-        <v>2.472245</v>
+        <v>2.7194695</v>
       </c>
       <c r="N12">
-        <v>62.327755</v>
+        <v>62.08053049999999</v>
       </c>
       <c r="O12">
-        <v>14.023744875</v>
+        <v>13.9681193625</v>
       </c>
       <c r="P12">
-        <v>48.304010125</v>
+        <v>48.1124111375</v>
       </c>
       <c r="Q12">
-        <v>51.004010125</v>
+        <v>50.8124111375</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1741612350839797</v>
+        <v>0.175304715726413</v>
       </c>
       <c r="T12">
-        <v>0.894991337892149</v>
+        <v>0.9029641909840932</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>26.21099446050047</v>
+        <v>23.82817678227316</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1603092719965075</v>
+        <v>0.1599751824174333</v>
       </c>
       <c r="C13">
-        <v>535.5735057873924</v>
+        <v>532.328259004909</v>
       </c>
       <c r="D13">
-        <v>570.6385057873924</v>
+        <v>572.308259004909</v>
       </c>
       <c r="E13">
-        <v>-298.635</v>
+        <v>-293.72</v>
       </c>
       <c r="F13">
-        <v>54.065</v>
+        <v>58.98</v>
       </c>
       <c r="G13">
         <v>19</v>
@@ -2353,28 +2353,28 @@
         <v>64.8</v>
       </c>
       <c r="M13">
-        <v>2.7194695</v>
+        <v>2.966693999999999</v>
       </c>
       <c r="N13">
-        <v>62.08053049999999</v>
+        <v>61.833306</v>
       </c>
       <c r="O13">
-        <v>13.9681193625</v>
+        <v>13.91249385</v>
       </c>
       <c r="P13">
-        <v>48.1124111375</v>
+        <v>47.92081215</v>
       </c>
       <c r="Q13">
-        <v>50.8124111375</v>
+        <v>50.62081215000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.175304715726413</v>
+        <v>0.1764741845652651</v>
       </c>
       <c r="T13">
-        <v>0.9029641909840932</v>
+        <v>0.9111182452826726</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>23.82817678227316</v>
+        <v>21.8424953837504</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1599751824174333</v>
+        <v>0.1596410928383591</v>
       </c>
       <c r="C14">
-        <v>532.328259004909</v>
+        <v>529.0928126755958</v>
       </c>
       <c r="D14">
-        <v>572.308259004909</v>
+        <v>573.9878126755958</v>
       </c>
       <c r="E14">
-        <v>-293.72</v>
+        <v>-288.805</v>
       </c>
       <c r="F14">
-        <v>58.98</v>
+        <v>63.895</v>
       </c>
       <c r="G14">
         <v>19</v>
@@ -2435,28 +2435,28 @@
         <v>64.8</v>
       </c>
       <c r="M14">
-        <v>2.966693999999999</v>
+        <v>3.2139185</v>
       </c>
       <c r="N14">
-        <v>61.833306</v>
+        <v>61.5860815</v>
       </c>
       <c r="O14">
-        <v>13.91249385</v>
+        <v>13.8568683375</v>
       </c>
       <c r="P14">
-        <v>47.92081215</v>
+        <v>47.7292131625</v>
       </c>
       <c r="Q14">
-        <v>50.62081215000001</v>
+        <v>50.42921316250001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1764741845652651</v>
+        <v>0.1776705377452403</v>
       </c>
       <c r="T14">
-        <v>0.9111182452826726</v>
+        <v>0.9194597491053572</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>21.8424953837504</v>
+        <v>20.16230343115421</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1596410928383591</v>
+        <v>0.1593070032592848</v>
       </c>
       <c r="C15">
-        <v>529.0928126755958</v>
+        <v>525.8672533376182</v>
       </c>
       <c r="D15">
-        <v>573.9878126755958</v>
+        <v>575.6772533376181</v>
       </c>
       <c r="E15">
-        <v>-288.805</v>
+        <v>-283.89</v>
       </c>
       <c r="F15">
-        <v>63.895</v>
+        <v>68.81</v>
       </c>
       <c r="G15">
         <v>19</v>
@@ -2517,28 +2517,28 @@
         <v>64.8</v>
       </c>
       <c r="M15">
-        <v>3.2139185</v>
+        <v>3.461143</v>
       </c>
       <c r="N15">
-        <v>61.5860815</v>
+        <v>61.338857</v>
       </c>
       <c r="O15">
-        <v>13.8568683375</v>
+        <v>13.801242825</v>
       </c>
       <c r="P15">
-        <v>47.7292131625</v>
+        <v>47.537614175</v>
       </c>
       <c r="Q15">
-        <v>50.42921316250001</v>
+        <v>50.237614175</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1776705377452403</v>
+        <v>0.1788947130921917</v>
       </c>
       <c r="T15">
-        <v>0.9194597491053572</v>
+        <v>0.9279952413890343</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>20.16230343115421</v>
+        <v>18.72213890035748</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1593070032592848</v>
+        <v>0.1589729136802106</v>
       </c>
       <c r="C16">
-        <v>525.8672533376182</v>
+        <v>522.6516685509936</v>
       </c>
       <c r="D16">
-        <v>575.6772533376181</v>
+        <v>577.3766685509936</v>
       </c>
       <c r="E16">
-        <v>-283.89</v>
+        <v>-278.975</v>
       </c>
       <c r="F16">
-        <v>68.81</v>
+        <v>73.72500000000001</v>
       </c>
       <c r="G16">
         <v>19</v>
@@ -2599,28 +2599,28 @@
         <v>64.8</v>
       </c>
       <c r="M16">
-        <v>3.461143</v>
+        <v>3.7083675</v>
       </c>
       <c r="N16">
-        <v>61.338857</v>
+        <v>61.0916325</v>
       </c>
       <c r="O16">
-        <v>13.801242825</v>
+        <v>13.7456173125</v>
       </c>
       <c r="P16">
-        <v>47.537614175</v>
+        <v>47.3460151875</v>
       </c>
       <c r="Q16">
-        <v>50.237614175</v>
+        <v>50.0460151875</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1788947130921917</v>
+        <v>0.1801476925649537</v>
       </c>
       <c r="T16">
-        <v>0.9279952413890343</v>
+        <v>0.9367315687852688</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>18.72213890035748</v>
+        <v>17.47399630700032</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1589729136802106</v>
+        <v>0.1586388241011364</v>
       </c>
       <c r="C17">
-        <v>522.6516685509936</v>
+        <v>519.4461469127194</v>
       </c>
       <c r="D17">
-        <v>577.3766685509936</v>
+        <v>579.0861469127194</v>
       </c>
       <c r="E17">
-        <v>-278.975</v>
+        <v>-274.06</v>
       </c>
       <c r="F17">
-        <v>73.72499999999999</v>
+        <v>78.64</v>
       </c>
       <c r="G17">
         <v>19</v>
@@ -2681,28 +2681,28 @@
         <v>64.8</v>
       </c>
       <c r="M17">
-        <v>3.7083675</v>
+        <v>3.955592</v>
       </c>
       <c r="N17">
-        <v>61.0916325</v>
+        <v>60.84440799999999</v>
       </c>
       <c r="O17">
-        <v>13.7456173125</v>
+        <v>13.6899918</v>
       </c>
       <c r="P17">
-        <v>47.3460151875</v>
+        <v>47.15441619999999</v>
       </c>
       <c r="Q17">
-        <v>50.0460151875</v>
+        <v>49.8544162</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1801476925649537</v>
+        <v>0.1814305048823052</v>
       </c>
       <c r="T17">
-        <v>0.9367315687852688</v>
+        <v>0.9456759039766515</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>17.47399630700032</v>
+        <v>16.3818715378128</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1586388241011364</v>
+        <v>0.1583047345220622</v>
       </c>
       <c r="C18">
-        <v>519.4461469127194</v>
+        <v>516.2507780721694</v>
       </c>
       <c r="D18">
-        <v>579.0861469127194</v>
+        <v>580.8057780721693</v>
       </c>
       <c r="E18">
-        <v>-274.06</v>
+        <v>-269.145</v>
       </c>
       <c r="F18">
-        <v>78.64</v>
+        <v>83.55500000000001</v>
       </c>
       <c r="G18">
         <v>19</v>
@@ -2763,28 +2763,28 @@
         <v>64.8</v>
       </c>
       <c r="M18">
-        <v>3.955592</v>
+        <v>4.2028165</v>
       </c>
       <c r="N18">
-        <v>60.84440799999999</v>
+        <v>60.5971835</v>
       </c>
       <c r="O18">
-        <v>13.6899918</v>
+        <v>13.6343662875</v>
       </c>
       <c r="P18">
-        <v>47.15441619999999</v>
+        <v>46.9628172125</v>
       </c>
       <c r="Q18">
-        <v>49.8544162</v>
+        <v>49.6628172125</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1814305048823052</v>
+        <v>0.1827442283398339</v>
       </c>
       <c r="T18">
-        <v>0.9456759039766515</v>
+        <v>0.9548357653172242</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>16.3818715378128</v>
+        <v>15.41823203558851</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1583047345220622</v>
+        <v>0.1579706449429879</v>
       </c>
       <c r="C19">
-        <v>516.2507780721694</v>
+        <v>513.0656527467659</v>
       </c>
       <c r="D19">
-        <v>580.8057780721693</v>
+        <v>582.5356527467659</v>
       </c>
       <c r="E19">
-        <v>-269.145</v>
+        <v>-264.23</v>
       </c>
       <c r="F19">
-        <v>83.55500000000001</v>
+        <v>88.47000000000001</v>
       </c>
       <c r="G19">
         <v>19</v>
@@ -2845,28 +2845,28 @@
         <v>64.8</v>
       </c>
       <c r="M19">
-        <v>4.2028165</v>
+        <v>4.450041000000001</v>
       </c>
       <c r="N19">
-        <v>60.5971835</v>
+        <v>60.349959</v>
       </c>
       <c r="O19">
-        <v>13.6343662875</v>
+        <v>13.578740775</v>
       </c>
       <c r="P19">
-        <v>46.9628172125</v>
+        <v>46.771218225</v>
       </c>
       <c r="Q19">
-        <v>49.6628172125</v>
+        <v>49.471218225</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1827442283398339</v>
+        <v>0.1840899938329121</v>
       </c>
       <c r="T19">
-        <v>0.9548357653172242</v>
+        <v>0.9642190379100061</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.41823203558851</v>
+        <v>14.56166358916693</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1579706449429879</v>
+        <v>0.1576365553639137</v>
       </c>
       <c r="C20">
-        <v>513.0656527467657</v>
+        <v>509.8908627379319</v>
       </c>
       <c r="D20">
-        <v>582.5356527467658</v>
+        <v>584.2758627379319</v>
       </c>
       <c r="E20">
-        <v>-264.23</v>
+        <v>-259.315</v>
       </c>
       <c r="F20">
-        <v>88.47</v>
+        <v>93.38500000000001</v>
       </c>
       <c r="G20">
         <v>19</v>
@@ -2927,28 +2927,28 @@
         <v>64.8</v>
       </c>
       <c r="M20">
-        <v>4.450041</v>
+        <v>4.6972655</v>
       </c>
       <c r="N20">
-        <v>60.349959</v>
+        <v>60.1027345</v>
       </c>
       <c r="O20">
-        <v>13.578740775</v>
+        <v>13.5231152625</v>
       </c>
       <c r="P20">
-        <v>46.771218225</v>
+        <v>46.5796192375</v>
       </c>
       <c r="Q20">
-        <v>49.471218225</v>
+        <v>49.2796192375</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1840899938329121</v>
+        <v>0.1854689881035972</v>
       </c>
       <c r="T20">
-        <v>0.9642190379100061</v>
+        <v>0.9738339962458195</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.56166358916693</v>
+        <v>13.79526024236867</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1576365553639137</v>
+        <v>0.1573024657848395</v>
       </c>
       <c r="C21">
-        <v>509.8908627379319</v>
+        <v>506.7265009473325</v>
       </c>
       <c r="D21">
-        <v>584.2758627379319</v>
+        <v>586.0265009473325</v>
       </c>
       <c r="E21">
-        <v>-259.315</v>
+        <v>-254.4</v>
       </c>
       <c r="F21">
-        <v>93.38500000000001</v>
+        <v>98.30000000000001</v>
       </c>
       <c r="G21">
         <v>19</v>
@@ -3009,28 +3009,28 @@
         <v>64.8</v>
       </c>
       <c r="M21">
-        <v>4.6972655</v>
+        <v>4.94449</v>
       </c>
       <c r="N21">
-        <v>60.1027345</v>
+        <v>59.85551</v>
       </c>
       <c r="O21">
-        <v>13.5231152625</v>
+        <v>13.46748975</v>
       </c>
       <c r="P21">
-        <v>46.5796192375</v>
+        <v>46.38802025</v>
       </c>
       <c r="Q21">
-        <v>49.2796192375</v>
+        <v>49.08802025</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1854689881035972</v>
+        <v>0.1868824572310494</v>
       </c>
       <c r="T21">
-        <v>0.9738339962458195</v>
+        <v>0.9836893285400284</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>13.79526024236867</v>
+        <v>13.10549723025024</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1573024657848395</v>
+        <v>0.1572125012057653</v>
       </c>
       <c r="C22">
-        <v>506.7265009473325</v>
+        <v>502.2847120045612</v>
       </c>
       <c r="D22">
-        <v>586.0265009473325</v>
+        <v>586.4997120045613</v>
       </c>
       <c r="E22">
-        <v>-254.4</v>
+        <v>-249.485</v>
       </c>
       <c r="F22">
-        <v>98.30000000000001</v>
+        <v>103.215</v>
       </c>
       <c r="G22">
         <v>19</v>
@@ -3091,45 +3091,45 @@
         <v>64.8</v>
       </c>
       <c r="M22">
-        <v>4.94449</v>
+        <v>5.346537</v>
       </c>
       <c r="N22">
-        <v>59.85551</v>
+        <v>59.453463</v>
       </c>
       <c r="O22">
-        <v>13.46748975</v>
+        <v>13.377029175</v>
       </c>
       <c r="P22">
-        <v>46.38802025</v>
+        <v>46.076433825</v>
       </c>
       <c r="Q22">
-        <v>49.08802025</v>
+        <v>48.776433825</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1868824572310494</v>
+        <v>0.1883317103870446</v>
       </c>
       <c r="T22">
-        <v>0.9836893285400284</v>
+        <v>0.9937941629176349</v>
       </c>
       <c r="U22">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V22">
         <v>0.225</v>
       </c>
       <c r="W22">
-        <v>0.0389825</v>
+        <v>0.040145</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y22">
-        <v>13.10549723025024</v>
+        <v>12.119994680669</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1572125012057653</v>
+        <v>0.156890036626691</v>
       </c>
       <c r="C23">
-        <v>502.2847120045613</v>
+        <v>499.0721633539496</v>
       </c>
       <c r="D23">
-        <v>586.4997120045613</v>
+        <v>588.2021633539496</v>
       </c>
       <c r="E23">
-        <v>-249.485</v>
+        <v>-244.57</v>
       </c>
       <c r="F23">
-        <v>103.215</v>
+        <v>108.13</v>
       </c>
       <c r="G23">
         <v>19</v>
@@ -3173,28 +3173,28 @@
         <v>64.8</v>
       </c>
       <c r="M23">
-        <v>5.346537</v>
+        <v>5.601134</v>
       </c>
       <c r="N23">
-        <v>59.453463</v>
+        <v>59.198866</v>
       </c>
       <c r="O23">
-        <v>13.377029175</v>
+        <v>13.31974485</v>
       </c>
       <c r="P23">
-        <v>46.076433825</v>
+        <v>45.87912115</v>
       </c>
       <c r="Q23">
-        <v>48.776433825</v>
+        <v>48.57912115</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1883317103870446</v>
+        <v>0.1898181238803731</v>
       </c>
       <c r="T23">
-        <v>0.9937941629176349</v>
+        <v>1.004158095612616</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>12.119994680669</v>
+        <v>11.56908583154768</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.156890036626691</v>
+        <v>0.1565675720476168</v>
       </c>
       <c r="C24">
-        <v>499.0721633539496</v>
+        <v>495.8695269953135</v>
       </c>
       <c r="D24">
-        <v>588.2021633539496</v>
+        <v>589.9145269953135</v>
       </c>
       <c r="E24">
-        <v>-244.57</v>
+        <v>-239.655</v>
       </c>
       <c r="F24">
-        <v>108.13</v>
+        <v>113.045</v>
       </c>
       <c r="G24">
         <v>19</v>
@@ -3255,28 +3255,28 @@
         <v>64.8</v>
       </c>
       <c r="M24">
-        <v>5.601134</v>
+        <v>5.855731</v>
       </c>
       <c r="N24">
-        <v>59.198866</v>
+        <v>58.944269</v>
       </c>
       <c r="O24">
-        <v>13.31974485</v>
+        <v>13.262460525</v>
       </c>
       <c r="P24">
-        <v>45.87912115</v>
+        <v>45.681808475</v>
       </c>
       <c r="Q24">
-        <v>48.57912115</v>
+        <v>48.381808475</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1898181238803731</v>
+        <v>0.1913431455163854</v>
       </c>
       <c r="T24">
-        <v>1.004158095612616</v>
+        <v>1.014791221364609</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.56908583154768</v>
+        <v>11.06608209974126</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1565675720476168</v>
+        <v>0.1562451074685426</v>
       </c>
       <c r="C25">
-        <v>495.8695269953135</v>
+        <v>492.6768897508705</v>
       </c>
       <c r="D25">
-        <v>589.9145269953135</v>
+        <v>591.6368897508705</v>
       </c>
       <c r="E25">
-        <v>-239.655</v>
+        <v>-234.74</v>
       </c>
       <c r="F25">
-        <v>113.045</v>
+        <v>117.96</v>
       </c>
       <c r="G25">
         <v>19</v>
@@ -3337,28 +3337,28 @@
         <v>64.8</v>
       </c>
       <c r="M25">
-        <v>5.855731</v>
+        <v>6.110328</v>
       </c>
       <c r="N25">
-        <v>58.944269</v>
+        <v>58.68967199999999</v>
       </c>
       <c r="O25">
-        <v>13.262460525</v>
+        <v>13.2051762</v>
       </c>
       <c r="P25">
-        <v>45.681808475</v>
+        <v>45.4844958</v>
       </c>
       <c r="Q25">
-        <v>48.381808475</v>
+        <v>48.1844958</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1913431455163854</v>
+        <v>0.1929082993007139</v>
       </c>
       <c r="T25">
-        <v>1.014791221364609</v>
+        <v>1.02570416621534</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.06608209974126</v>
+        <v>10.60499534558538</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1562451074685426</v>
+        <v>0.1559226428894683</v>
       </c>
       <c r="C26">
-        <v>492.6768897508705</v>
+        <v>489.4943394597811</v>
       </c>
       <c r="D26">
-        <v>591.6368897508705</v>
+        <v>593.3693394597811</v>
       </c>
       <c r="E26">
-        <v>-234.74</v>
+        <v>-229.825</v>
       </c>
       <c r="F26">
-        <v>117.96</v>
+        <v>122.875</v>
       </c>
       <c r="G26">
         <v>19</v>
@@ -3419,28 +3419,28 @@
         <v>64.8</v>
       </c>
       <c r="M26">
-        <v>6.110327999999999</v>
+        <v>6.364924999999999</v>
       </c>
       <c r="N26">
-        <v>58.689672</v>
+        <v>58.435075</v>
       </c>
       <c r="O26">
-        <v>13.2051762</v>
+        <v>13.147891875</v>
       </c>
       <c r="P26">
-        <v>45.4844958</v>
+        <v>45.287183125</v>
       </c>
       <c r="Q26">
-        <v>48.18449580000001</v>
+        <v>47.987183125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1929082993007139</v>
+        <v>0.1945151905192911</v>
       </c>
       <c r="T26">
-        <v>1.02570416621534</v>
+        <v>1.036908122928756</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.60499534558538</v>
+        <v>10.18079553176196</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1559226428894683</v>
+        <v>0.1559427283103941</v>
       </c>
       <c r="C27">
-        <v>489.4943394597811</v>
+        <v>484.4711337422513</v>
       </c>
       <c r="D27">
-        <v>593.3693394597811</v>
+        <v>593.2611337422513</v>
       </c>
       <c r="E27">
-        <v>-229.825</v>
+        <v>-224.91</v>
       </c>
       <c r="F27">
-        <v>122.875</v>
+        <v>127.79</v>
       </c>
       <c r="G27">
         <v>19</v>
@@ -3501,45 +3501,45 @@
         <v>64.8</v>
       </c>
       <c r="M27">
-        <v>6.364924999999999</v>
+        <v>6.836765</v>
       </c>
       <c r="N27">
-        <v>58.435075</v>
+        <v>57.963235</v>
       </c>
       <c r="O27">
-        <v>13.147891875</v>
+        <v>13.041727875</v>
       </c>
       <c r="P27">
-        <v>45.287183125</v>
+        <v>44.921507125</v>
       </c>
       <c r="Q27">
-        <v>47.987183125</v>
+        <v>47.621507125</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1945151905192911</v>
+        <v>0.1961655112302623</v>
       </c>
       <c r="T27">
-        <v>1.036908122928756</v>
+        <v>1.048414889283076</v>
       </c>
       <c r="U27">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V27">
         <v>0.225</v>
       </c>
       <c r="W27">
-        <v>0.040145</v>
+        <v>0.0414625</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>10.18079553176196</v>
+        <v>9.478166940065952</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1559427283103941</v>
+        <v>0.1556334387313199</v>
       </c>
       <c r="C28">
-        <v>484.4711337422513</v>
+        <v>481.2267496171224</v>
       </c>
       <c r="D28">
-        <v>593.2611337422513</v>
+        <v>594.9317496171225</v>
       </c>
       <c r="E28">
-        <v>-224.91</v>
+        <v>-219.995</v>
       </c>
       <c r="F28">
-        <v>127.79</v>
+        <v>132.705</v>
       </c>
       <c r="G28">
         <v>19</v>
@@ -3583,28 +3583,28 @@
         <v>64.8</v>
       </c>
       <c r="M28">
-        <v>6.836765</v>
+        <v>7.099717500000001</v>
       </c>
       <c r="N28">
-        <v>57.963235</v>
+        <v>57.7002825</v>
       </c>
       <c r="O28">
-        <v>13.041727875</v>
+        <v>12.9825635625</v>
       </c>
       <c r="P28">
-        <v>44.921507125</v>
+        <v>44.7177189375</v>
       </c>
       <c r="Q28">
-        <v>47.621507125</v>
+        <v>47.4177189375</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1961655112302623</v>
+        <v>0.1978610462072875</v>
       </c>
       <c r="T28">
-        <v>1.048414889283076</v>
+        <v>1.060236909510116</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>9.478166940065952</v>
+        <v>9.127123720063508</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1556334387313199</v>
+        <v>0.1553241491522456</v>
       </c>
       <c r="C29">
-        <v>481.2267496171224</v>
+        <v>477.991800928557</v>
       </c>
       <c r="D29">
-        <v>594.9317496171225</v>
+        <v>596.611800928557</v>
       </c>
       <c r="E29">
-        <v>-219.995</v>
+        <v>-215.08</v>
       </c>
       <c r="F29">
-        <v>132.705</v>
+        <v>137.62</v>
       </c>
       <c r="G29">
         <v>19</v>
@@ -3665,28 +3665,28 @@
         <v>64.8</v>
       </c>
       <c r="M29">
-        <v>7.099717500000001</v>
+        <v>7.36267</v>
       </c>
       <c r="N29">
-        <v>57.7002825</v>
+        <v>57.43733</v>
       </c>
       <c r="O29">
-        <v>12.9825635625</v>
+        <v>12.92339925</v>
       </c>
       <c r="P29">
-        <v>44.7177189375</v>
+        <v>44.51393075</v>
       </c>
       <c r="Q29">
-        <v>47.4177189375</v>
+        <v>47.21393075</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1978610462072875</v>
+        <v>0.199603679378119</v>
       </c>
       <c r="T29">
-        <v>1.060236909510116</v>
+        <v>1.072387319187908</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>9.127123720063508</v>
+        <v>8.801155015775526</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1553241491522456</v>
+        <v>0.1550148595731714</v>
       </c>
       <c r="C30">
-        <v>477.991800928557</v>
+        <v>474.7663678382344</v>
       </c>
       <c r="D30">
-        <v>596.611800928557</v>
+        <v>598.3013678382345</v>
       </c>
       <c r="E30">
-        <v>-215.08</v>
+        <v>-210.165</v>
       </c>
       <c r="F30">
-        <v>137.62</v>
+        <v>142.535</v>
       </c>
       <c r="G30">
         <v>19</v>
@@ -3747,28 +3747,28 @@
         <v>64.8</v>
       </c>
       <c r="M30">
-        <v>7.36267</v>
+        <v>7.625622500000001</v>
       </c>
       <c r="N30">
-        <v>57.43733</v>
+        <v>57.1743775</v>
       </c>
       <c r="O30">
-        <v>12.92339925</v>
+        <v>12.8642349375</v>
       </c>
       <c r="P30">
-        <v>44.51393075</v>
+        <v>44.3101425625</v>
       </c>
       <c r="Q30">
-        <v>47.21393075</v>
+        <v>47.0101425625</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.199603679378119</v>
+        <v>0.2013954008072837</v>
       </c>
       <c r="T30">
-        <v>1.072387319187908</v>
+        <v>1.084879993927046</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.801155015775526</v>
+        <v>8.497666911783266</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1550148595731714</v>
+        <v>0.1547055699940972</v>
       </c>
       <c r="C31">
-        <v>474.7663678382347</v>
+        <v>471.550531418465</v>
       </c>
       <c r="D31">
-        <v>598.3013678382347</v>
+        <v>600.000531418465</v>
       </c>
       <c r="E31">
-        <v>-210.165</v>
+        <v>-205.25</v>
       </c>
       <c r="F31">
-        <v>142.535</v>
+        <v>147.45</v>
       </c>
       <c r="G31">
         <v>19</v>
@@ -3829,28 +3829,28 @@
         <v>64.8</v>
       </c>
       <c r="M31">
-        <v>7.6256225</v>
+        <v>7.888574999999999</v>
       </c>
       <c r="N31">
-        <v>57.1743775</v>
+        <v>56.91142499999999</v>
       </c>
       <c r="O31">
-        <v>12.8642349375</v>
+        <v>12.805070625</v>
       </c>
       <c r="P31">
-        <v>44.3101425625</v>
+        <v>44.106354375</v>
       </c>
       <c r="Q31">
-        <v>47.0101425625</v>
+        <v>46.806354375</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2013954008072837</v>
+        <v>0.2032383142772817</v>
       </c>
       <c r="T31">
-        <v>1.084879993927045</v>
+        <v>1.097729602230159</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.497666911783268</v>
+        <v>8.214411348057158</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1547055699940972</v>
+        <v>0.154396280415023</v>
       </c>
       <c r="C32">
-        <v>471.550531418465</v>
+        <v>468.3443736651566</v>
       </c>
       <c r="D32">
-        <v>600.000531418465</v>
+        <v>601.7093736651566</v>
       </c>
       <c r="E32">
-        <v>-205.25</v>
+        <v>-200.335</v>
       </c>
       <c r="F32">
-        <v>147.45</v>
+        <v>152.365</v>
       </c>
       <c r="G32">
         <v>19</v>
@@ -3911,28 +3911,28 @@
         <v>64.8</v>
       </c>
       <c r="M32">
-        <v>7.888574999999999</v>
+        <v>8.1515275</v>
       </c>
       <c r="N32">
-        <v>56.91142499999999</v>
+        <v>56.6484725</v>
       </c>
       <c r="O32">
-        <v>12.805070625</v>
+        <v>12.7459063125</v>
       </c>
       <c r="P32">
-        <v>44.106354375</v>
+        <v>43.9025661875</v>
       </c>
       <c r="Q32">
-        <v>46.806354375</v>
+        <v>46.6025661875</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2032383142772817</v>
+        <v>0.2051346455290188</v>
       </c>
       <c r="T32">
-        <v>1.097729602230159</v>
+        <v>1.110951662947855</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.214411348057158</v>
+        <v>7.949430336829508</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.154396280415023</v>
+        <v>0.1540869908359487</v>
       </c>
       <c r="C33">
-        <v>468.3443736651566</v>
+        <v>465.1479775110042</v>
       </c>
       <c r="D33">
-        <v>601.7093736651566</v>
+        <v>603.4279775110042</v>
       </c>
       <c r="E33">
-        <v>-200.335</v>
+        <v>-195.42</v>
       </c>
       <c r="F33">
-        <v>152.365</v>
+        <v>157.28</v>
       </c>
       <c r="G33">
         <v>19</v>
@@ -3993,28 +3993,28 @@
         <v>64.8</v>
       </c>
       <c r="M33">
-        <v>8.1515275</v>
+        <v>8.414479999999999</v>
       </c>
       <c r="N33">
-        <v>56.6484725</v>
+        <v>56.38552</v>
       </c>
       <c r="O33">
-        <v>12.7459063125</v>
+        <v>12.686742</v>
       </c>
       <c r="P33">
-        <v>43.9025661875</v>
+        <v>43.698778</v>
       </c>
       <c r="Q33">
-        <v>46.6025661875</v>
+        <v>46.398778</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2051346455290188</v>
+        <v>0.2070867512293364</v>
       </c>
       <c r="T33">
-        <v>1.110951662947855</v>
+        <v>1.124562607804307</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.949430336829508</v>
+        <v>7.701010638803587</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1540869908359487</v>
+        <v>0.1539823012568745</v>
       </c>
       <c r="C34">
-        <v>465.1479775110042</v>
+        <v>460.8169235006278</v>
       </c>
       <c r="D34">
-        <v>603.4279775110042</v>
+        <v>604.0119235006279</v>
       </c>
       <c r="E34">
-        <v>-195.42</v>
+        <v>-190.505</v>
       </c>
       <c r="F34">
-        <v>157.28</v>
+        <v>162.195</v>
       </c>
       <c r="G34">
         <v>19</v>
@@ -4075,45 +4075,45 @@
         <v>64.8</v>
       </c>
       <c r="M34">
-        <v>8.414479999999999</v>
+        <v>8.807188500000001</v>
       </c>
       <c r="N34">
-        <v>56.38552</v>
+        <v>55.99281149999999</v>
       </c>
       <c r="O34">
-        <v>12.686742</v>
+        <v>12.5983825875</v>
       </c>
       <c r="P34">
-        <v>43.698778</v>
+        <v>43.3944289125</v>
       </c>
       <c r="Q34">
-        <v>46.398778</v>
+        <v>46.0944289125</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2070867512293364</v>
+        <v>0.2090971287416037</v>
       </c>
       <c r="T34">
-        <v>1.124562607804307</v>
+        <v>1.138579849522146</v>
       </c>
       <c r="U34">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V34">
         <v>0.225</v>
       </c>
       <c r="W34">
-        <v>0.0414625</v>
+        <v>0.0420825</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y34">
-        <v>7.701010638803587</v>
+        <v>7.357626102813627</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1539823012568745</v>
+        <v>0.1536792116778003</v>
       </c>
       <c r="C35">
-        <v>460.8169235006278</v>
+        <v>457.5989114263127</v>
       </c>
       <c r="D35">
-        <v>604.0119235006279</v>
+        <v>605.7089114263127</v>
       </c>
       <c r="E35">
-        <v>-190.505</v>
+        <v>-185.59</v>
       </c>
       <c r="F35">
-        <v>162.195</v>
+        <v>167.11</v>
       </c>
       <c r="G35">
         <v>19</v>
@@ -4157,28 +4157,28 @@
         <v>64.8</v>
       </c>
       <c r="M35">
-        <v>8.807188500000001</v>
+        <v>9.074073</v>
       </c>
       <c r="N35">
-        <v>55.99281149999999</v>
+        <v>55.725927</v>
       </c>
       <c r="O35">
-        <v>12.5983825875</v>
+        <v>12.538333575</v>
       </c>
       <c r="P35">
-        <v>43.3944289125</v>
+        <v>43.187593425</v>
       </c>
       <c r="Q35">
-        <v>46.0944289125</v>
+        <v>45.88759342500001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2090971287416037</v>
+        <v>0.2111684267845459</v>
       </c>
       <c r="T35">
-        <v>1.138579849522146</v>
+        <v>1.153021856140525</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.357626102813627</v>
+        <v>7.141225335083814</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1536792116778003</v>
+        <v>0.153376122098726</v>
       </c>
       <c r="C36">
-        <v>457.5989114263127</v>
+        <v>454.3904616850889</v>
       </c>
       <c r="D36">
-        <v>605.7089114263127</v>
+        <v>607.4154616850889</v>
       </c>
       <c r="E36">
-        <v>-185.59</v>
+        <v>-180.675</v>
       </c>
       <c r="F36">
-        <v>167.11</v>
+        <v>172.025</v>
       </c>
       <c r="G36">
         <v>19</v>
@@ -4239,28 +4239,28 @@
         <v>64.8</v>
       </c>
       <c r="M36">
-        <v>9.074073</v>
+        <v>9.3409575</v>
       </c>
       <c r="N36">
-        <v>55.725927</v>
+        <v>55.4590425</v>
       </c>
       <c r="O36">
-        <v>12.538333575</v>
+        <v>12.4782845625</v>
       </c>
       <c r="P36">
-        <v>43.187593425</v>
+        <v>42.98075793749999</v>
       </c>
       <c r="Q36">
-        <v>45.88759342500001</v>
+        <v>45.6807579375</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2111684267845459</v>
+        <v>0.2133034570749631</v>
       </c>
       <c r="T36">
-        <v>1.153021856140525</v>
+        <v>1.167908232193316</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.141225335083814</v>
+        <v>6.937190325509992</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.153376122098726</v>
+        <v>0.1530730325196518</v>
       </c>
       <c r="C37">
-        <v>454.3904616850889</v>
+        <v>451.1916553292983</v>
       </c>
       <c r="D37">
-        <v>607.4154616850889</v>
+        <v>609.1316553292984</v>
       </c>
       <c r="E37">
-        <v>-180.675</v>
+        <v>-175.76</v>
       </c>
       <c r="F37">
-        <v>172.025</v>
+        <v>176.94</v>
       </c>
       <c r="G37">
         <v>19</v>
@@ -4321,28 +4321,28 @@
         <v>64.8</v>
       </c>
       <c r="M37">
-        <v>9.3409575</v>
+        <v>9.607842000000002</v>
       </c>
       <c r="N37">
-        <v>55.4590425</v>
+        <v>55.19215799999999</v>
       </c>
       <c r="O37">
-        <v>12.4782845625</v>
+        <v>12.41823555</v>
       </c>
       <c r="P37">
-        <v>42.98075793749999</v>
+        <v>42.77392244999999</v>
       </c>
       <c r="Q37">
-        <v>45.6807579375</v>
+        <v>45.47392245</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2133034570749631</v>
+        <v>0.215505207061956</v>
       </c>
       <c r="T37">
-        <v>1.167908232193316</v>
+        <v>1.183259807497757</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.937190325509992</v>
+        <v>6.744490594245824</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1530730325196518</v>
+        <v>0.1527699429405776</v>
       </c>
       <c r="C38">
-        <v>451.1916553292984</v>
+        <v>448.0025743299011</v>
       </c>
       <c r="D38">
-        <v>609.1316553292984</v>
+        <v>610.8575743299011</v>
       </c>
       <c r="E38">
-        <v>-175.76</v>
+        <v>-170.845</v>
       </c>
       <c r="F38">
-        <v>176.94</v>
+        <v>181.855</v>
       </c>
       <c r="G38">
         <v>19</v>
@@ -4403,28 +4403,28 @@
         <v>64.8</v>
       </c>
       <c r="M38">
-        <v>9.607842</v>
+        <v>9.8747265</v>
       </c>
       <c r="N38">
-        <v>55.192158</v>
+        <v>54.9252735</v>
       </c>
       <c r="O38">
-        <v>12.41823555</v>
+        <v>12.3581865375</v>
       </c>
       <c r="P38">
-        <v>42.77392245</v>
+        <v>42.5670869625</v>
       </c>
       <c r="Q38">
-        <v>45.47392245</v>
+        <v>45.2670869625</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.215505207061956</v>
+        <v>0.2177768538739327</v>
       </c>
       <c r="T38">
-        <v>1.183259807497757</v>
+        <v>1.199098734399164</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.744490594245826</v>
+        <v>6.562207064671614</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1527699429405776</v>
+        <v>0.1524668533615033</v>
       </c>
       <c r="C39">
-        <v>448.0025743299011</v>
+        <v>444.8233015895261</v>
       </c>
       <c r="D39">
-        <v>610.8575743299011</v>
+        <v>612.593301589526</v>
       </c>
       <c r="E39">
-        <v>-170.845</v>
+        <v>-165.93</v>
       </c>
       <c r="F39">
-        <v>181.855</v>
+        <v>186.77</v>
       </c>
       <c r="G39">
         <v>19</v>
@@ -4485,28 +4485,28 @@
         <v>64.8</v>
       </c>
       <c r="M39">
-        <v>9.8747265</v>
+        <v>10.141611</v>
       </c>
       <c r="N39">
-        <v>54.9252735</v>
+        <v>54.658389</v>
       </c>
       <c r="O39">
-        <v>12.3581865375</v>
+        <v>12.298137525</v>
       </c>
       <c r="P39">
-        <v>42.5670869625</v>
+        <v>42.360251475</v>
       </c>
       <c r="Q39">
-        <v>45.2670869625</v>
+        <v>45.060251475</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2177768538739327</v>
+        <v>0.220121779615328</v>
       </c>
       <c r="T39">
-        <v>1.199098734399164</v>
+        <v>1.215448594426423</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.562207064671614</v>
+        <v>6.389517405074992</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1524668533615033</v>
+        <v>0.1521637637824291</v>
       </c>
       <c r="C40">
-        <v>444.8233015895261</v>
+        <v>441.6539209557441</v>
       </c>
       <c r="D40">
-        <v>612.593301589526</v>
+        <v>614.3389209557441</v>
       </c>
       <c r="E40">
-        <v>-165.93</v>
+        <v>-161.015</v>
       </c>
       <c r="F40">
-        <v>186.77</v>
+        <v>191.685</v>
       </c>
       <c r="G40">
         <v>19</v>
@@ -4567,28 +4567,28 @@
         <v>64.8</v>
       </c>
       <c r="M40">
-        <v>10.141611</v>
+        <v>10.4084955</v>
       </c>
       <c r="N40">
-        <v>54.658389</v>
+        <v>54.3915045</v>
       </c>
       <c r="O40">
-        <v>12.298137525</v>
+        <v>12.2380885125</v>
       </c>
       <c r="P40">
-        <v>42.360251475</v>
+        <v>42.1534159875</v>
       </c>
       <c r="Q40">
-        <v>45.060251475</v>
+        <v>44.8534159875</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.220121779615328</v>
+        <v>0.2225435881679166</v>
       </c>
       <c r="T40">
-        <v>1.215448594426423</v>
+        <v>1.232334515438182</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.389517405074992</v>
+        <v>6.225683625457684</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1521637637824291</v>
+        <v>0.1521706742033549</v>
       </c>
       <c r="C41">
-        <v>441.6539209557441</v>
+        <v>436.6990101385319</v>
       </c>
       <c r="D41">
-        <v>614.3389209557441</v>
+        <v>614.2990101385319</v>
       </c>
       <c r="E41">
-        <v>-161.015</v>
+        <v>-156.1</v>
       </c>
       <c r="F41">
-        <v>191.685</v>
+        <v>196.6</v>
       </c>
       <c r="G41">
         <v>19</v>
@@ -4649,45 +4649,45 @@
         <v>64.8</v>
       </c>
       <c r="M41">
-        <v>10.4084955</v>
+        <v>10.87198</v>
       </c>
       <c r="N41">
-        <v>54.3915045</v>
+        <v>53.92802</v>
       </c>
       <c r="O41">
-        <v>12.2380885125</v>
+        <v>12.1338045</v>
       </c>
       <c r="P41">
-        <v>42.1534159875</v>
+        <v>41.79421549999999</v>
       </c>
       <c r="Q41">
-        <v>44.8534159875</v>
+        <v>44.4942155</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2225435881679166</v>
+        <v>0.2250461236722582</v>
       </c>
       <c r="T41">
-        <v>1.232334515438182</v>
+        <v>1.249783300483666</v>
       </c>
       <c r="U41">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V41">
         <v>0.225</v>
       </c>
       <c r="W41">
-        <v>0.0420825</v>
+        <v>0.0428575</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>6.225683625457684</v>
+        <v>5.960275865113805</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1521706742033549</v>
+        <v>0.1518753346242807</v>
       </c>
       <c r="C42">
-        <v>436.6990101385319</v>
+        <v>433.4943682695963</v>
       </c>
       <c r="D42">
-        <v>614.2990101385319</v>
+        <v>616.0093682695963</v>
       </c>
       <c r="E42">
-        <v>-156.1</v>
+        <v>-151.185</v>
       </c>
       <c r="F42">
-        <v>196.6</v>
+        <v>201.515</v>
       </c>
       <c r="G42">
         <v>19</v>
@@ -4731,28 +4731,28 @@
         <v>64.8</v>
       </c>
       <c r="M42">
-        <v>10.87198</v>
+        <v>11.1437795</v>
       </c>
       <c r="N42">
-        <v>53.92802</v>
+        <v>53.6562205</v>
       </c>
       <c r="O42">
-        <v>12.1338045</v>
+        <v>12.0726496125</v>
       </c>
       <c r="P42">
-        <v>41.79421549999999</v>
+        <v>41.5835708875</v>
       </c>
       <c r="Q42">
-        <v>44.4942155</v>
+        <v>44.2835708875</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2250461236722582</v>
+        <v>0.2276334908886113</v>
       </c>
       <c r="T42">
-        <v>1.249783300483666</v>
+        <v>1.26782356976798</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.960275865113805</v>
+        <v>5.814903283037859</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1518753346242807</v>
+        <v>0.1515799950452064</v>
       </c>
       <c r="C43">
-        <v>433.4943682695963</v>
+        <v>430.2992770997375</v>
       </c>
       <c r="D43">
-        <v>616.0093682695963</v>
+        <v>617.7292770997375</v>
       </c>
       <c r="E43">
-        <v>-151.185</v>
+        <v>-146.27</v>
       </c>
       <c r="F43">
-        <v>201.515</v>
+        <v>206.43</v>
       </c>
       <c r="G43">
         <v>19</v>
@@ -4813,28 +4813,28 @@
         <v>64.8</v>
       </c>
       <c r="M43">
-        <v>11.1437795</v>
+        <v>11.415579</v>
       </c>
       <c r="N43">
-        <v>53.6562205</v>
+        <v>53.384421</v>
       </c>
       <c r="O43">
-        <v>12.0726496125</v>
+        <v>12.011494725</v>
       </c>
       <c r="P43">
-        <v>41.5835708875</v>
+        <v>41.372926275</v>
       </c>
       <c r="Q43">
-        <v>44.2835708875</v>
+        <v>44.072926275</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2276334908886113</v>
+        <v>0.230310077664149</v>
       </c>
       <c r="T43">
-        <v>1.26782356976798</v>
+        <v>1.286485917303478</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.814903283037859</v>
+        <v>5.676453204870291</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1515799950452064</v>
+        <v>0.1512846554661322</v>
       </c>
       <c r="C44">
-        <v>430.2992770997373</v>
+        <v>427.1138168500854</v>
       </c>
       <c r="D44">
-        <v>617.7292770997373</v>
+        <v>619.4588168500854</v>
       </c>
       <c r="E44">
-        <v>-146.27</v>
+        <v>-141.355</v>
       </c>
       <c r="F44">
-        <v>206.43</v>
+        <v>211.345</v>
       </c>
       <c r="G44">
         <v>19</v>
@@ -4895,28 +4895,28 @@
         <v>64.8</v>
       </c>
       <c r="M44">
-        <v>11.415579</v>
+        <v>11.6873785</v>
       </c>
       <c r="N44">
-        <v>53.384421</v>
+        <v>53.1126215</v>
       </c>
       <c r="O44">
-        <v>12.011494725</v>
+        <v>11.9503398375</v>
       </c>
       <c r="P44">
-        <v>41.372926275</v>
+        <v>41.16228166249999</v>
       </c>
       <c r="Q44">
-        <v>44.072926275</v>
+        <v>43.8622816625</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.230310077664149</v>
+        <v>0.2330805797651442</v>
       </c>
       <c r="T44">
-        <v>1.286485917303478</v>
+        <v>1.305803084050748</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.676453204870292</v>
+        <v>5.544442665222145</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1512846554661322</v>
+        <v>0.150989315887058</v>
       </c>
       <c r="C45">
-        <v>427.1138168500854</v>
+        <v>423.9380686427177</v>
       </c>
       <c r="D45">
-        <v>619.4588168500854</v>
+        <v>621.1980686427177</v>
       </c>
       <c r="E45">
-        <v>-141.355</v>
+        <v>-136.44</v>
       </c>
       <c r="F45">
-        <v>211.345</v>
+        <v>216.26</v>
       </c>
       <c r="G45">
         <v>19</v>
@@ -4977,28 +4977,28 @@
         <v>64.8</v>
       </c>
       <c r="M45">
-        <v>11.6873785</v>
+        <v>11.959178</v>
       </c>
       <c r="N45">
-        <v>53.1126215</v>
+        <v>52.840822</v>
       </c>
       <c r="O45">
-        <v>11.9503398375</v>
+        <v>11.88918495</v>
       </c>
       <c r="P45">
-        <v>41.16228166249999</v>
+        <v>40.95163705</v>
       </c>
       <c r="Q45">
-        <v>43.8622816625</v>
+        <v>43.65163705</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2330805797651442</v>
+        <v>0.2359500283697464</v>
       </c>
       <c r="T45">
-        <v>1.305803084050748</v>
+        <v>1.32581014961042</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.544442665222145</v>
+        <v>5.418432604648914</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.150989315887058</v>
+        <v>0.1506939763079838</v>
       </c>
       <c r="C46">
-        <v>423.9380686427177</v>
+        <v>420.7721145133401</v>
       </c>
       <c r="D46">
-        <v>621.1980686427177</v>
+        <v>622.9471145133401</v>
       </c>
       <c r="E46">
-        <v>-136.44</v>
+        <v>-131.525</v>
       </c>
       <c r="F46">
-        <v>216.26</v>
+        <v>221.175</v>
       </c>
       <c r="G46">
         <v>19</v>
@@ -5059,28 +5059,28 @@
         <v>64.8</v>
       </c>
       <c r="M46">
-        <v>11.959178</v>
+        <v>12.2309775</v>
       </c>
       <c r="N46">
-        <v>52.840822</v>
+        <v>52.5690225</v>
       </c>
       <c r="O46">
-        <v>11.88918495</v>
+        <v>11.8280300625</v>
       </c>
       <c r="P46">
-        <v>40.95163705</v>
+        <v>40.7409924375</v>
       </c>
       <c r="Q46">
-        <v>43.65163705</v>
+        <v>43.4409924375</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2359500283697464</v>
+        <v>0.2389238205599705</v>
       </c>
       <c r="T46">
-        <v>1.32581014961042</v>
+        <v>1.346544744826807</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.418432604648914</v>
+        <v>5.298022991212271</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1506939763079838</v>
+        <v>0.1503986367289095</v>
       </c>
       <c r="C47">
-        <v>420.7721145133401</v>
+        <v>417.6160374241878</v>
       </c>
       <c r="D47">
-        <v>622.9471145133401</v>
+        <v>624.7060374241878</v>
       </c>
       <c r="E47">
-        <v>-131.525</v>
+        <v>-126.61</v>
       </c>
       <c r="F47">
-        <v>221.175</v>
+        <v>226.09</v>
       </c>
       <c r="G47">
         <v>19</v>
@@ -5141,28 +5141,28 @@
         <v>64.8</v>
       </c>
       <c r="M47">
-        <v>12.2309775</v>
+        <v>12.502777</v>
       </c>
       <c r="N47">
-        <v>52.5690225</v>
+        <v>52.297223</v>
       </c>
       <c r="O47">
-        <v>11.8280300625</v>
+        <v>11.766875175</v>
       </c>
       <c r="P47">
-        <v>40.7409924375</v>
+        <v>40.53034782499999</v>
       </c>
       <c r="Q47">
-        <v>43.4409924375</v>
+        <v>43.230347825</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2389238205599705</v>
+        <v>0.2420077532016843</v>
       </c>
       <c r="T47">
-        <v>1.346544744826807</v>
+        <v>1.368047288014172</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.298022991212271</v>
+        <v>5.182848578359831</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1503986367289095</v>
+        <v>0.1501032971498353</v>
       </c>
       <c r="C48">
-        <v>417.6160374241878</v>
+        <v>414.4699212771394</v>
       </c>
       <c r="D48">
-        <v>624.7060374241878</v>
+        <v>626.4749212771394</v>
       </c>
       <c r="E48">
-        <v>-126.61</v>
+        <v>-121.695</v>
       </c>
       <c r="F48">
-        <v>226.09</v>
+        <v>231.005</v>
       </c>
       <c r="G48">
         <v>19</v>
@@ -5223,28 +5223,28 @@
         <v>64.8</v>
       </c>
       <c r="M48">
-        <v>12.502777</v>
+        <v>12.7745765</v>
       </c>
       <c r="N48">
-        <v>52.297223</v>
+        <v>52.0254235</v>
       </c>
       <c r="O48">
-        <v>11.766875175</v>
+        <v>11.7057202875</v>
       </c>
       <c r="P48">
-        <v>40.53034782499999</v>
+        <v>40.3197032125</v>
       </c>
       <c r="Q48">
-        <v>43.230347825</v>
+        <v>43.0197032125</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2420077532016843</v>
+        <v>0.2452080606600666</v>
       </c>
       <c r="T48">
-        <v>1.368047288014172</v>
+        <v>1.390361247925588</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.182848578359831</v>
+        <v>5.072575204352175</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1501032971498353</v>
+        <v>0.1498079575707611</v>
       </c>
       <c r="C49">
-        <v>414.4699212771394</v>
+        <v>411.3338509270625</v>
       </c>
       <c r="D49">
-        <v>626.4749212771394</v>
+        <v>628.2538509270626</v>
       </c>
       <c r="E49">
-        <v>-121.695</v>
+        <v>-116.78</v>
       </c>
       <c r="F49">
-        <v>231.005</v>
+        <v>235.92</v>
       </c>
       <c r="G49">
         <v>19</v>
@@ -5305,28 +5305,28 @@
         <v>64.8</v>
       </c>
       <c r="M49">
-        <v>12.7745765</v>
+        <v>13.046376</v>
       </c>
       <c r="N49">
-        <v>52.0254235</v>
+        <v>51.75362399999999</v>
       </c>
       <c r="O49">
-        <v>11.7057202875</v>
+        <v>11.6445654</v>
       </c>
       <c r="P49">
-        <v>40.3197032125</v>
+        <v>40.1090586</v>
       </c>
       <c r="Q49">
-        <v>43.0197032125</v>
+        <v>42.8090586</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2452080606600666</v>
+        <v>0.2485314568668482</v>
       </c>
       <c r="T49">
-        <v>1.390361247925588</v>
+        <v>1.413533437064366</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.072575204352175</v>
+        <v>4.966896554261504</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1498079575707611</v>
+        <v>0.1495126179916868</v>
       </c>
       <c r="C50">
-        <v>411.3338509270626</v>
+        <v>408.2079121953784</v>
       </c>
       <c r="D50">
-        <v>628.2538509270626</v>
+        <v>630.0429121953784</v>
       </c>
       <c r="E50">
-        <v>-116.78</v>
+        <v>-111.865</v>
       </c>
       <c r="F50">
-        <v>235.92</v>
+        <v>240.835</v>
       </c>
       <c r="G50">
         <v>19</v>
@@ -5387,28 +5387,28 @@
         <v>64.8</v>
       </c>
       <c r="M50">
-        <v>13.046376</v>
+        <v>13.3181755</v>
       </c>
       <c r="N50">
-        <v>51.75362399999999</v>
+        <v>51.48182449999999</v>
       </c>
       <c r="O50">
-        <v>11.6445654</v>
+        <v>11.5834105125</v>
       </c>
       <c r="P50">
-        <v>40.1090586</v>
+        <v>39.89841398749999</v>
       </c>
       <c r="Q50">
-        <v>42.8090586</v>
+        <v>42.5984139875</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2485314568668482</v>
+        <v>0.2519851823366408</v>
       </c>
       <c r="T50">
-        <v>1.413533437064366</v>
+        <v>1.437614339502704</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.966896554261504</v>
+        <v>4.865531318460249</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1495126179916868</v>
+        <v>0.1492172784126126</v>
       </c>
       <c r="C51">
-        <v>408.2079121953784</v>
+        <v>405.0921918838661</v>
       </c>
       <c r="D51">
-        <v>630.0429121953784</v>
+        <v>631.8421918838661</v>
       </c>
       <c r="E51">
-        <v>-111.865</v>
+        <v>-106.95</v>
       </c>
       <c r="F51">
-        <v>240.835</v>
+        <v>245.75</v>
       </c>
       <c r="G51">
         <v>19</v>
@@ -5469,28 +5469,28 @@
         <v>64.8</v>
       </c>
       <c r="M51">
-        <v>13.3181755</v>
+        <v>13.589975</v>
       </c>
       <c r="N51">
-        <v>51.48182449999999</v>
+        <v>51.21002499999999</v>
       </c>
       <c r="O51">
-        <v>11.5834105125</v>
+        <v>11.522255625</v>
       </c>
       <c r="P51">
-        <v>39.89841398749999</v>
+        <v>39.68776937499999</v>
       </c>
       <c r="Q51">
-        <v>42.5984139875</v>
+        <v>42.387769375</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2519851823366408</v>
+        <v>0.2555770568252252</v>
       </c>
       <c r="T51">
-        <v>1.437614339502704</v>
+        <v>1.462658478038576</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.865531318460249</v>
+        <v>4.768220692091044</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1492172784126126</v>
+        <v>0.1489219388335384</v>
       </c>
       <c r="C52">
-        <v>405.0921918838661</v>
+        <v>401.9867777886999</v>
       </c>
       <c r="D52">
-        <v>631.8421918838661</v>
+        <v>633.6517777886999</v>
       </c>
       <c r="E52">
-        <v>-106.95</v>
+        <v>-102.035</v>
       </c>
       <c r="F52">
-        <v>245.75</v>
+        <v>250.665</v>
       </c>
       <c r="G52">
         <v>19</v>
@@ -5551,28 +5551,28 @@
         <v>64.8</v>
       </c>
       <c r="M52">
-        <v>13.589975</v>
+        <v>13.8617745</v>
       </c>
       <c r="N52">
-        <v>51.21002499999999</v>
+        <v>50.9382255</v>
       </c>
       <c r="O52">
-        <v>11.522255625</v>
+        <v>11.4611007375</v>
       </c>
       <c r="P52">
-        <v>39.68776937499999</v>
+        <v>39.4771247625</v>
       </c>
       <c r="Q52">
-        <v>42.387769375</v>
+        <v>42.1771247625</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2555770568252252</v>
+        <v>0.2593155384357926</v>
       </c>
       <c r="T52">
-        <v>1.462658478038576</v>
+        <v>1.488724826310606</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.768220692091044</v>
+        <v>4.674726168716711</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1489219388335384</v>
+        <v>0.1486265992544642</v>
       </c>
       <c r="C53">
-        <v>401.9867777886999</v>
+        <v>398.8917587147307</v>
       </c>
       <c r="D53">
-        <v>633.6517777886999</v>
+        <v>635.4717587147308</v>
       </c>
       <c r="E53">
-        <v>-102.035</v>
+        <v>-97.11999999999998</v>
       </c>
       <c r="F53">
-        <v>250.665</v>
+        <v>255.58</v>
       </c>
       <c r="G53">
         <v>19</v>
@@ -5633,28 +5633,28 @@
         <v>64.8</v>
       </c>
       <c r="M53">
-        <v>13.8617745</v>
+        <v>14.133574</v>
       </c>
       <c r="N53">
-        <v>50.9382255</v>
+        <v>50.66642599999999</v>
       </c>
       <c r="O53">
-        <v>11.4611007375</v>
+        <v>11.39994585</v>
       </c>
       <c r="P53">
-        <v>39.4771247625</v>
+        <v>39.26648014999999</v>
       </c>
       <c r="Q53">
-        <v>42.1771247625</v>
+        <v>41.96648015</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2593155384357926</v>
+        <v>0.263209790113467</v>
       </c>
       <c r="T53">
-        <v>1.488724826310606</v>
+        <v>1.515877272427304</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.674726168716711</v>
+        <v>4.584827588549081</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1486265992544642</v>
+        <v>0.1493581346753899</v>
       </c>
       <c r="C54">
-        <v>398.8917587147307</v>
+        <v>389.4877815623807</v>
       </c>
       <c r="D54">
-        <v>635.4717587147308</v>
+        <v>630.9827815623808</v>
       </c>
       <c r="E54">
-        <v>-97.11999999999998</v>
+        <v>-92.20499999999998</v>
       </c>
       <c r="F54">
-        <v>255.58</v>
+        <v>260.495</v>
       </c>
       <c r="G54">
         <v>19</v>
@@ -5715,45 +5715,45 @@
         <v>64.8</v>
       </c>
       <c r="M54">
-        <v>14.133574</v>
+        <v>15.056611</v>
       </c>
       <c r="N54">
-        <v>50.66642599999999</v>
+        <v>49.74338899999999</v>
       </c>
       <c r="O54">
-        <v>11.39994585</v>
+        <v>11.192262525</v>
       </c>
       <c r="P54">
-        <v>39.26648014999999</v>
+        <v>38.551126475</v>
       </c>
       <c r="Q54">
-        <v>41.96648015</v>
+        <v>41.251126475</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.263209790113467</v>
+        <v>0.2672697546284892</v>
       </c>
       <c r="T54">
-        <v>1.515877272427304</v>
+        <v>1.54418514178301</v>
       </c>
       <c r="U54">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V54">
         <v>0.225</v>
       </c>
       <c r="W54">
-        <v>0.0428575</v>
+        <v>0.044795</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>4.584827588549081</v>
+        <v>4.303757332908447</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1493581346753899</v>
+        <v>0.1490821700963157</v>
       </c>
       <c r="C55">
-        <v>389.4877815623807</v>
+        <v>386.2587346901526</v>
       </c>
       <c r="D55">
-        <v>630.9827815623808</v>
+        <v>632.6687346901526</v>
       </c>
       <c r="E55">
-        <v>-92.20499999999998</v>
+        <v>-87.28999999999996</v>
       </c>
       <c r="F55">
-        <v>260.495</v>
+        <v>265.41</v>
       </c>
       <c r="G55">
         <v>19</v>
@@ -5797,28 +5797,28 @@
         <v>64.8</v>
       </c>
       <c r="M55">
-        <v>15.056611</v>
+        <v>15.340698</v>
       </c>
       <c r="N55">
-        <v>49.74338899999999</v>
+        <v>49.45930199999999</v>
       </c>
       <c r="O55">
-        <v>11.192262525</v>
+        <v>11.12834295</v>
       </c>
       <c r="P55">
-        <v>38.551126475</v>
+        <v>38.33095905</v>
       </c>
       <c r="Q55">
-        <v>41.251126475</v>
+        <v>41.03095905</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2672697546284892</v>
+        <v>0.2715062393398167</v>
       </c>
       <c r="T55">
-        <v>1.54418514178301</v>
+        <v>1.573723788067225</v>
       </c>
       <c r="U55">
         <v>0.0578</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.303757332908447</v>
+        <v>4.224058123039772</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1490821700963157</v>
+        <v>0.1488062055172414</v>
       </c>
       <c r="C56">
-        <v>386.2587346901526</v>
+        <v>383.0387215133784</v>
       </c>
       <c r="D56">
-        <v>632.6687346901526</v>
+        <v>634.3637215133784</v>
       </c>
       <c r="E56">
-        <v>-87.28999999999996</v>
+        <v>-82.37499999999994</v>
       </c>
       <c r="F56">
-        <v>265.41</v>
+        <v>270.325</v>
       </c>
       <c r="G56">
         <v>19</v>
@@ -5879,28 +5879,28 @@
         <v>64.8</v>
       </c>
       <c r="M56">
-        <v>15.340698</v>
+        <v>15.624785</v>
       </c>
       <c r="N56">
-        <v>49.45930199999999</v>
+        <v>49.17521499999999</v>
       </c>
       <c r="O56">
-        <v>11.12834295</v>
+        <v>11.064423375</v>
       </c>
       <c r="P56">
-        <v>38.33095905</v>
+        <v>38.110791625</v>
       </c>
       <c r="Q56">
-        <v>41.03095905</v>
+        <v>40.810791625</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2715062393398167</v>
+        <v>0.2759310122605366</v>
       </c>
       <c r="T56">
-        <v>1.573723788067225</v>
+        <v>1.604575263075183</v>
       </c>
       <c r="U56">
         <v>0.0578</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.224058123039772</v>
+        <v>4.147257066257231</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1488062055172414</v>
+        <v>0.1485302409381672</v>
       </c>
       <c r="C57">
-        <v>383.0387215133784</v>
+        <v>379.8278148337937</v>
       </c>
       <c r="D57">
-        <v>634.3637215133784</v>
+        <v>636.0678148337937</v>
       </c>
       <c r="E57">
-        <v>-82.37499999999994</v>
+        <v>-77.45999999999998</v>
       </c>
       <c r="F57">
-        <v>270.325</v>
+        <v>275.24</v>
       </c>
       <c r="G57">
         <v>19</v>
@@ -5961,28 +5961,28 @@
         <v>64.8</v>
       </c>
       <c r="M57">
-        <v>15.624785</v>
+        <v>15.908872</v>
       </c>
       <c r="N57">
-        <v>49.17521499999999</v>
+        <v>48.89112799999999</v>
       </c>
       <c r="O57">
-        <v>11.064423375</v>
+        <v>11.0005038</v>
       </c>
       <c r="P57">
-        <v>38.110791625</v>
+        <v>37.8906242</v>
       </c>
       <c r="Q57">
-        <v>40.810791625</v>
+        <v>40.5906242</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2759310122605366</v>
+        <v>0.2805569112231074</v>
       </c>
       <c r="T57">
-        <v>1.604575263075183</v>
+        <v>1.63682907785623</v>
       </c>
       <c r="U57">
         <v>0.0578</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.147257066257231</v>
+        <v>4.07319890435978</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1485302409381672</v>
+        <v>0.148254276359093</v>
       </c>
       <c r="C58">
-        <v>379.8278148337937</v>
+        <v>376.6260882375124</v>
       </c>
       <c r="D58">
-        <v>636.0678148337937</v>
+        <v>637.7810882375124</v>
       </c>
       <c r="E58">
-        <v>-77.45999999999998</v>
+        <v>-72.54499999999996</v>
       </c>
       <c r="F58">
-        <v>275.24</v>
+        <v>280.155</v>
       </c>
       <c r="G58">
         <v>19</v>
@@ -6043,28 +6043,28 @@
         <v>64.8</v>
       </c>
       <c r="M58">
-        <v>15.908872</v>
+        <v>16.192959</v>
       </c>
       <c r="N58">
-        <v>48.89112799999999</v>
+        <v>48.607041</v>
       </c>
       <c r="O58">
-        <v>11.0005038</v>
+        <v>10.936584225</v>
       </c>
       <c r="P58">
-        <v>37.8906242</v>
+        <v>37.670456775</v>
       </c>
       <c r="Q58">
-        <v>40.5906242</v>
+        <v>40.370456775</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2805569112231074</v>
+        <v>0.2853979682769605</v>
       </c>
       <c r="T58">
-        <v>1.63682907785623</v>
+        <v>1.670583070068954</v>
       </c>
       <c r="U58">
         <v>0.0578</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.07319890435978</v>
+        <v>4.001739274458732</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.148254276359093</v>
+        <v>0.1495515617800187</v>
       </c>
       <c r="C59">
-        <v>376.6260882375124</v>
+        <v>363.7364217041356</v>
       </c>
       <c r="D59">
-        <v>637.7810882375124</v>
+        <v>629.8064217041357</v>
       </c>
       <c r="E59">
-        <v>-72.54499999999996</v>
+        <v>-67.62999999999994</v>
       </c>
       <c r="F59">
-        <v>280.155</v>
+        <v>285.0700000000001</v>
       </c>
       <c r="G59">
         <v>19</v>
@@ -6125,45 +6125,45 @@
         <v>64.8</v>
       </c>
       <c r="M59">
-        <v>16.192959</v>
+        <v>17.474791</v>
       </c>
       <c r="N59">
-        <v>48.607041</v>
+        <v>47.32520899999999</v>
       </c>
       <c r="O59">
-        <v>10.936584225</v>
+        <v>10.648172025</v>
       </c>
       <c r="P59">
-        <v>37.670456775</v>
+        <v>36.67703697499999</v>
       </c>
       <c r="Q59">
-        <v>40.370456775</v>
+        <v>39.377036975</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2853979682769605</v>
+        <v>0.2904695518571875</v>
       </c>
       <c r="T59">
-        <v>1.670583070068954</v>
+        <v>1.705944395244188</v>
       </c>
       <c r="U59">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V59">
         <v>0.225</v>
       </c>
       <c r="W59">
-        <v>0.044795</v>
+        <v>0.0475075</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>4.001739274458732</v>
+        <v>3.708198856283888</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1495515617800187</v>
+        <v>0.1493027222009445</v>
       </c>
       <c r="C60">
-        <v>363.7364217041357</v>
+        <v>360.3355921678925</v>
       </c>
       <c r="D60">
-        <v>629.8064217041357</v>
+        <v>631.3205921678924</v>
       </c>
       <c r="E60">
-        <v>-67.63</v>
+        <v>-62.71500000000003</v>
       </c>
       <c r="F60">
-        <v>285.07</v>
+        <v>289.985</v>
       </c>
       <c r="G60">
         <v>19</v>
@@ -6207,28 +6207,28 @@
         <v>64.8</v>
       </c>
       <c r="M60">
-        <v>17.474791</v>
+        <v>17.7760805</v>
       </c>
       <c r="N60">
-        <v>47.325209</v>
+        <v>47.0239195</v>
       </c>
       <c r="O60">
-        <v>10.648172025</v>
+        <v>10.5803818875</v>
       </c>
       <c r="P60">
-        <v>36.677036975</v>
+        <v>36.44353761249999</v>
       </c>
       <c r="Q60">
-        <v>39.377036975</v>
+        <v>39.1435376125</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2904695518571875</v>
+        <v>0.2957885297584013</v>
       </c>
       <c r="T60">
-        <v>1.705944395244188</v>
+        <v>1.743030663110897</v>
       </c>
       <c r="U60">
         <v>0.0613</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.708198856283889</v>
+        <v>3.645348028211281</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1493027222009445</v>
+        <v>0.1490538826218703</v>
       </c>
       <c r="C61">
-        <v>360.3355921678925</v>
+        <v>356.9420608664717</v>
       </c>
       <c r="D61">
-        <v>631.3205921678924</v>
+        <v>632.8420608664717</v>
       </c>
       <c r="E61">
-        <v>-62.71500000000003</v>
+        <v>-57.80000000000001</v>
       </c>
       <c r="F61">
-        <v>289.985</v>
+        <v>294.9</v>
       </c>
       <c r="G61">
         <v>19</v>
@@ -6289,28 +6289,28 @@
         <v>64.8</v>
       </c>
       <c r="M61">
-        <v>17.7760805</v>
+        <v>18.07737</v>
       </c>
       <c r="N61">
-        <v>47.0239195</v>
+        <v>46.72263</v>
       </c>
       <c r="O61">
-        <v>10.5803818875</v>
+        <v>10.51259175</v>
       </c>
       <c r="P61">
-        <v>36.44353761249999</v>
+        <v>36.21003825</v>
       </c>
       <c r="Q61">
-        <v>39.1435376125</v>
+        <v>38.91003825</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2957885297584013</v>
+        <v>0.3013734565546757</v>
       </c>
       <c r="T61">
-        <v>1.743030663110897</v>
+        <v>1.781971244370941</v>
       </c>
       <c r="U61">
         <v>0.0613</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.645348028211281</v>
+        <v>3.584592227741093</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1490538826218703</v>
+        <v>0.1488050430427961</v>
       </c>
       <c r="C62">
-        <v>356.9420608664717</v>
+        <v>353.5558806930994</v>
       </c>
       <c r="D62">
-        <v>632.8420608664717</v>
+        <v>634.3708806930994</v>
       </c>
       <c r="E62">
-        <v>-57.80000000000001</v>
+        <v>-52.88499999999999</v>
       </c>
       <c r="F62">
-        <v>294.9</v>
+        <v>299.815</v>
       </c>
       <c r="G62">
         <v>19</v>
@@ -6371,28 +6371,28 @@
         <v>64.8</v>
       </c>
       <c r="M62">
-        <v>18.07737</v>
+        <v>18.3786595</v>
       </c>
       <c r="N62">
-        <v>46.72263</v>
+        <v>46.4213405</v>
       </c>
       <c r="O62">
-        <v>10.51259175</v>
+        <v>10.4448016125</v>
       </c>
       <c r="P62">
-        <v>36.21003825</v>
+        <v>35.9765388875</v>
       </c>
       <c r="Q62">
-        <v>38.91003825</v>
+        <v>38.6765388875</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3013734565546757</v>
+        <v>0.3072447898533233</v>
       </c>
       <c r="T62">
-        <v>1.781971244370941</v>
+        <v>1.822908778516117</v>
       </c>
       <c r="U62">
         <v>0.0613</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.584592227741093</v>
+        <v>3.525828420728943</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1488050430427961</v>
+        <v>0.1499016034637218</v>
       </c>
       <c r="C63">
-        <v>353.5558806930994</v>
+        <v>341.9586973567181</v>
       </c>
       <c r="D63">
-        <v>634.3708806930994</v>
+        <v>627.6886973567181</v>
       </c>
       <c r="E63">
-        <v>-52.88499999999999</v>
+        <v>-47.96999999999997</v>
       </c>
       <c r="F63">
-        <v>299.815</v>
+        <v>304.73</v>
       </c>
       <c r="G63">
         <v>19</v>
@@ -6453,45 +6453,45 @@
         <v>64.8</v>
       </c>
       <c r="M63">
-        <v>18.3786595</v>
+        <v>19.533193</v>
       </c>
       <c r="N63">
-        <v>46.4213405</v>
+        <v>45.266807</v>
       </c>
       <c r="O63">
-        <v>10.4448016125</v>
+        <v>10.185031575</v>
       </c>
       <c r="P63">
-        <v>35.9765388875</v>
+        <v>35.081775425</v>
       </c>
       <c r="Q63">
-        <v>38.6765388875</v>
+        <v>37.78177542500001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3072447898533233</v>
+        <v>0.3134251406940048</v>
       </c>
       <c r="T63">
-        <v>1.822908778516117</v>
+        <v>1.866000919721564</v>
       </c>
       <c r="U63">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V63">
         <v>0.225</v>
       </c>
       <c r="W63">
-        <v>0.0475075</v>
+        <v>0.04967750000000001</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y63">
-        <v>3.525828420728943</v>
+        <v>3.317429976758024</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1499016034637218</v>
+        <v>0.1496744638846476</v>
       </c>
       <c r="C64">
-        <v>341.9586973567181</v>
+        <v>338.4162478486808</v>
       </c>
       <c r="D64">
-        <v>627.6886973567181</v>
+        <v>629.0612478486808</v>
       </c>
       <c r="E64">
-        <v>-47.96999999999997</v>
+        <v>-43.05500000000001</v>
       </c>
       <c r="F64">
-        <v>304.73</v>
+        <v>309.645</v>
       </c>
       <c r="G64">
         <v>19</v>
@@ -6535,28 +6535,28 @@
         <v>64.8</v>
       </c>
       <c r="M64">
-        <v>19.533193</v>
+        <v>19.8482445</v>
       </c>
       <c r="N64">
-        <v>45.266807</v>
+        <v>44.9517555</v>
       </c>
       <c r="O64">
-        <v>10.185031575</v>
+        <v>10.1141449875</v>
       </c>
       <c r="P64">
-        <v>35.081775425</v>
+        <v>34.8376105125</v>
       </c>
       <c r="Q64">
-        <v>37.78177542500001</v>
+        <v>37.5376105125</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3134251406940048</v>
+        <v>0.3199395645531017</v>
       </c>
       <c r="T64">
-        <v>1.866000919721564</v>
+        <v>1.911422365857035</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.317429976758024</v>
+        <v>3.264772358079325</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1496744638846476</v>
+        <v>0.1494473243055734</v>
       </c>
       <c r="C65">
-        <v>338.4162478486808</v>
+        <v>334.8798141359011</v>
       </c>
       <c r="D65">
-        <v>629.0612478486808</v>
+        <v>630.4398141359011</v>
       </c>
       <c r="E65">
-        <v>-43.05500000000001</v>
+        <v>-38.13999999999999</v>
       </c>
       <c r="F65">
-        <v>309.645</v>
+        <v>314.56</v>
       </c>
       <c r="G65">
         <v>19</v>
@@ -6617,28 +6617,28 @@
         <v>64.8</v>
       </c>
       <c r="M65">
-        <v>19.8482445</v>
+        <v>20.163296</v>
       </c>
       <c r="N65">
-        <v>44.9517555</v>
+        <v>44.63670399999999</v>
       </c>
       <c r="O65">
-        <v>10.1141449875</v>
+        <v>10.0432584</v>
       </c>
       <c r="P65">
-        <v>34.8376105125</v>
+        <v>34.5934456</v>
       </c>
       <c r="Q65">
-        <v>37.5376105125</v>
+        <v>37.2934456</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3199395645531017</v>
+        <v>0.3268159008488151</v>
       </c>
       <c r="T65">
-        <v>1.911422365857035</v>
+        <v>1.9593672256667</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.264772358079325</v>
+        <v>3.213760289984335</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1494473243055734</v>
+        <v>0.1492201847264992</v>
       </c>
       <c r="C66">
-        <v>334.8798141359011</v>
+        <v>331.3494358554731</v>
       </c>
       <c r="D66">
-        <v>630.4398141359011</v>
+        <v>631.8244358554731</v>
       </c>
       <c r="E66">
-        <v>-38.13999999999999</v>
+        <v>-33.22499999999997</v>
       </c>
       <c r="F66">
-        <v>314.56</v>
+        <v>319.475</v>
       </c>
       <c r="G66">
         <v>19</v>
@@ -6699,28 +6699,28 @@
         <v>64.8</v>
       </c>
       <c r="M66">
-        <v>20.163296</v>
+        <v>20.4783475</v>
       </c>
       <c r="N66">
-        <v>44.63670399999999</v>
+        <v>44.3216525</v>
       </c>
       <c r="O66">
-        <v>10.0432584</v>
+        <v>9.9723718125</v>
       </c>
       <c r="P66">
-        <v>34.5934456</v>
+        <v>34.3492806875</v>
       </c>
       <c r="Q66">
-        <v>37.2934456</v>
+        <v>37.0492806875</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3268159008488151</v>
+        <v>0.3340851706471406</v>
       </c>
       <c r="T66">
-        <v>1.9593672256667</v>
+        <v>2.010051791751203</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.213760289984335</v>
+        <v>3.164317823984577</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1492201847264992</v>
+        <v>0.148993045147425</v>
       </c>
       <c r="C67">
-        <v>331.3494358554731</v>
+        <v>327.8251529934741</v>
       </c>
       <c r="D67">
-        <v>631.8244358554731</v>
+        <v>633.2151529934741</v>
       </c>
       <c r="E67">
-        <v>-33.22499999999997</v>
+        <v>-28.30999999999995</v>
       </c>
       <c r="F67">
-        <v>319.475</v>
+        <v>324.39</v>
       </c>
       <c r="G67">
         <v>19</v>
@@ -6781,28 +6781,28 @@
         <v>64.8</v>
       </c>
       <c r="M67">
-        <v>20.4783475</v>
+        <v>20.793399</v>
       </c>
       <c r="N67">
-        <v>44.3216525</v>
+        <v>44.00660099999999</v>
       </c>
       <c r="O67">
-        <v>9.9723718125</v>
+        <v>9.901485224999998</v>
       </c>
       <c r="P67">
-        <v>34.3492806875</v>
+        <v>34.10511577499999</v>
       </c>
       <c r="Q67">
-        <v>37.0492806875</v>
+        <v>36.80511577499999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3340851706471406</v>
+        <v>0.3417820445512499</v>
       </c>
       <c r="T67">
-        <v>2.010051791751203</v>
+        <v>2.063717802899499</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.164317823984577</v>
+        <v>3.116373614530264</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.148993045147425</v>
+        <v>0.1487659055683507</v>
       </c>
       <c r="C68">
-        <v>327.8251529934741</v>
+        <v>324.3070058888131</v>
       </c>
       <c r="D68">
-        <v>633.2151529934741</v>
+        <v>634.6120058888131</v>
       </c>
       <c r="E68">
-        <v>-28.30999999999995</v>
+        <v>-23.39499999999998</v>
       </c>
       <c r="F68">
-        <v>324.39</v>
+        <v>329.305</v>
       </c>
       <c r="G68">
         <v>19</v>
@@ -6863,28 +6863,28 @@
         <v>64.8</v>
       </c>
       <c r="M68">
-        <v>20.793399</v>
+        <v>21.1084505</v>
       </c>
       <c r="N68">
-        <v>44.00660099999999</v>
+        <v>43.69154949999999</v>
       </c>
       <c r="O68">
-        <v>9.901485224999998</v>
+        <v>9.8305986375</v>
       </c>
       <c r="P68">
-        <v>34.10511577499999</v>
+        <v>33.86095086249999</v>
       </c>
       <c r="Q68">
-        <v>36.80511577499999</v>
+        <v>36.56095086249999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3417820445512499</v>
+        <v>0.3499453956616689</v>
       </c>
       <c r="T68">
-        <v>2.063717802899499</v>
+        <v>2.120636299571935</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.116373614530264</v>
+        <v>3.069860575507425</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1487659055683507</v>
+        <v>0.1485387659892765</v>
       </c>
       <c r="C69">
-        <v>324.3070058888131</v>
+        <v>320.7950352371322</v>
       </c>
       <c r="D69">
-        <v>634.6120058888131</v>
+        <v>636.0150352371322</v>
       </c>
       <c r="E69">
-        <v>-23.39499999999998</v>
+        <v>-18.47999999999996</v>
       </c>
       <c r="F69">
-        <v>329.305</v>
+        <v>334.22</v>
       </c>
       <c r="G69">
         <v>19</v>
@@ -6945,28 +6945,28 @@
         <v>64.8</v>
       </c>
       <c r="M69">
-        <v>21.1084505</v>
+        <v>21.423502</v>
       </c>
       <c r="N69">
-        <v>43.69154949999999</v>
+        <v>43.376498</v>
       </c>
       <c r="O69">
-        <v>9.8305986375</v>
+        <v>9.759712049999999</v>
       </c>
       <c r="P69">
-        <v>33.86095086249999</v>
+        <v>33.61678595</v>
       </c>
       <c r="Q69">
-        <v>36.56095086249999</v>
+        <v>36.31678595</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3499453956616689</v>
+        <v>0.3586189562164891</v>
       </c>
       <c r="T69">
-        <v>2.120636299571935</v>
+        <v>2.181112202286398</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.069860575507425</v>
+        <v>3.024715567044081</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1485387659892765</v>
+        <v>0.1524826764102023</v>
       </c>
       <c r="C70">
-        <v>320.7950352371322</v>
+        <v>292.3674424737833</v>
       </c>
       <c r="D70">
-        <v>636.0150352371322</v>
+        <v>612.5024424737834</v>
       </c>
       <c r="E70">
-        <v>-18.47999999999996</v>
+        <v>-13.56499999999994</v>
       </c>
       <c r="F70">
-        <v>334.22</v>
+        <v>339.135</v>
       </c>
       <c r="G70">
         <v>19</v>
@@ -7027,45 +7027,45 @@
         <v>64.8</v>
       </c>
       <c r="M70">
-        <v>21.423502</v>
+        <v>24.38380650000001</v>
       </c>
       <c r="N70">
-        <v>43.376498</v>
+        <v>40.41619349999999</v>
       </c>
       <c r="O70">
-        <v>9.759712049999999</v>
+        <v>9.093643537499998</v>
       </c>
       <c r="P70">
-        <v>33.61678595</v>
+        <v>31.32254996249999</v>
       </c>
       <c r="Q70">
-        <v>36.31678595</v>
+        <v>34.02254996249999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3586189562164891</v>
+        <v>0.3678521013232331</v>
       </c>
       <c r="T70">
-        <v>2.181112202286398</v>
+        <v>2.24548977614373</v>
       </c>
       <c r="U70">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V70">
         <v>0.225</v>
       </c>
       <c r="W70">
-        <v>0.04967750000000001</v>
+        <v>0.05572250000000001</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y70">
-        <v>3.024715567044081</v>
+        <v>2.657501403646719</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1524826764102023</v>
+        <v>0.152315986831128</v>
       </c>
       <c r="C71">
-        <v>292.3674424737833</v>
+        <v>288.4109631367875</v>
       </c>
       <c r="D71">
-        <v>612.5024424737834</v>
+        <v>613.4609631367875</v>
       </c>
       <c r="E71">
-        <v>-13.56499999999994</v>
+        <v>-8.649999999999977</v>
       </c>
       <c r="F71">
-        <v>339.135</v>
+        <v>344.05</v>
       </c>
       <c r="G71">
         <v>19</v>
@@ -7109,28 +7109,28 @@
         <v>64.8</v>
       </c>
       <c r="M71">
-        <v>24.38380650000001</v>
+        <v>24.737195</v>
       </c>
       <c r="N71">
-        <v>40.41619349999999</v>
+        <v>40.062805</v>
       </c>
       <c r="O71">
-        <v>9.093643537499998</v>
+        <v>9.014131125</v>
       </c>
       <c r="P71">
-        <v>31.32254996249999</v>
+        <v>31.048673875</v>
       </c>
       <c r="Q71">
-        <v>34.02254996249999</v>
+        <v>33.748673875</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3678521013232331</v>
+        <v>0.3777007894370935</v>
       </c>
       <c r="T71">
-        <v>2.24548977614373</v>
+        <v>2.314159188258217</v>
       </c>
       <c r="U71">
         <v>0.07190000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.657501403646719</v>
+        <v>2.619537097880337</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.152315986831128</v>
+        <v>0.1521492972520538</v>
       </c>
       <c r="C72">
-        <v>288.4109631367875</v>
+        <v>284.4574885287361</v>
       </c>
       <c r="D72">
-        <v>613.4609631367875</v>
+        <v>614.4224885287362</v>
       </c>
       <c r="E72">
-        <v>-8.649999999999977</v>
+        <v>-3.734999999999957</v>
       </c>
       <c r="F72">
-        <v>344.05</v>
+        <v>348.965</v>
       </c>
       <c r="G72">
         <v>19</v>
@@ -7191,28 +7191,28 @@
         <v>64.8</v>
       </c>
       <c r="M72">
-        <v>24.737195</v>
+        <v>25.0905835</v>
       </c>
       <c r="N72">
-        <v>40.062805</v>
+        <v>39.70941649999999</v>
       </c>
       <c r="O72">
-        <v>9.014131125</v>
+        <v>8.934618712499997</v>
       </c>
       <c r="P72">
-        <v>31.048673875</v>
+        <v>30.77479778749999</v>
       </c>
       <c r="Q72">
-        <v>33.748673875</v>
+        <v>33.47479778749999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3777007894370935</v>
+        <v>0.3882286974208752</v>
       </c>
       <c r="T72">
-        <v>2.314159188258217</v>
+        <v>2.387564421897841</v>
       </c>
       <c r="U72">
         <v>0.07190000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.619537097880337</v>
+        <v>2.582642209177797</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1521492972520538</v>
+        <v>0.1519826076729796</v>
       </c>
       <c r="C73">
-        <v>284.457488528736</v>
+        <v>280.5070328004497</v>
       </c>
       <c r="D73">
-        <v>614.4224885287359</v>
+        <v>615.3870328004497</v>
       </c>
       <c r="E73">
-        <v>-3.735000000000014</v>
+        <v>1.180000000000007</v>
       </c>
       <c r="F73">
-        <v>348.965</v>
+        <v>353.88</v>
       </c>
       <c r="G73">
         <v>19</v>
@@ -7273,28 +7273,28 @@
         <v>64.8</v>
       </c>
       <c r="M73">
-        <v>25.0905835</v>
+        <v>25.443972</v>
       </c>
       <c r="N73">
-        <v>39.7094165</v>
+        <v>39.35602799999999</v>
       </c>
       <c r="O73">
-        <v>8.934618712499999</v>
+        <v>8.855106299999999</v>
       </c>
       <c r="P73">
-        <v>30.7747977875</v>
+        <v>30.5009217</v>
       </c>
       <c r="Q73">
-        <v>33.4747977875</v>
+        <v>33.20092169999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3882286974208751</v>
+        <v>0.3995085988320699</v>
       </c>
       <c r="T73">
-        <v>2.387564421897841</v>
+        <v>2.466212886511724</v>
       </c>
       <c r="U73">
         <v>0.07190000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.582642209177798</v>
+        <v>2.546772178494773</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1519826076729796</v>
+        <v>0.1518159180939053</v>
       </c>
       <c r="C74">
-        <v>280.5070328004497</v>
+        <v>276.5596101917468</v>
       </c>
       <c r="D74">
-        <v>615.3870328004497</v>
+        <v>616.3546101917468</v>
       </c>
       <c r="E74">
-        <v>1.180000000000007</v>
+        <v>6.095000000000027</v>
       </c>
       <c r="F74">
-        <v>353.88</v>
+        <v>358.795</v>
       </c>
       <c r="G74">
         <v>19</v>
@@ -7355,28 +7355,28 @@
         <v>64.8</v>
       </c>
       <c r="M74">
-        <v>25.443972</v>
+        <v>25.7973605</v>
       </c>
       <c r="N74">
-        <v>39.35602799999999</v>
+        <v>39.00263949999999</v>
       </c>
       <c r="O74">
-        <v>8.855106299999999</v>
+        <v>8.775593887499999</v>
       </c>
       <c r="P74">
-        <v>30.5009217</v>
+        <v>30.22704561249999</v>
       </c>
       <c r="Q74">
-        <v>33.20092169999999</v>
+        <v>32.9270456125</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3995085988320699</v>
+        <v>0.4116240484959456</v>
       </c>
       <c r="T74">
-        <v>2.466212886511724</v>
+        <v>2.550687163319228</v>
       </c>
       <c r="U74">
         <v>0.07190000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.546772178494773</v>
+        <v>2.511884888378406</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1518159180939053</v>
+        <v>0.1538858785148311</v>
       </c>
       <c r="C75">
-        <v>276.5596101917468</v>
+        <v>259.840758792445</v>
       </c>
       <c r="D75">
-        <v>616.3546101917468</v>
+        <v>604.550758792445</v>
       </c>
       <c r="E75">
-        <v>6.095000000000027</v>
+        <v>11.00999999999999</v>
       </c>
       <c r="F75">
-        <v>358.795</v>
+        <v>363.71</v>
       </c>
       <c r="G75">
         <v>19</v>
@@ -7437,45 +7437,45 @@
         <v>64.8</v>
       </c>
       <c r="M75">
-        <v>25.7973605</v>
+        <v>27.569218</v>
       </c>
       <c r="N75">
-        <v>39.00263949999999</v>
+        <v>37.230782</v>
       </c>
       <c r="O75">
-        <v>8.775593887499999</v>
+        <v>8.37692595</v>
       </c>
       <c r="P75">
-        <v>30.22704561249999</v>
+        <v>28.85385605</v>
       </c>
       <c r="Q75">
-        <v>32.9270456125</v>
+        <v>31.55385605</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4116240484959456</v>
+        <v>0.4246714558262735</v>
       </c>
       <c r="T75">
-        <v>2.550687163319228</v>
+        <v>2.641659461419617</v>
       </c>
       <c r="U75">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V75">
         <v>0.225</v>
       </c>
       <c r="W75">
-        <v>0.05572250000000001</v>
+        <v>0.05874500000000001</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y75">
-        <v>2.511884888378406</v>
+        <v>2.350447517227366</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1538858785148311</v>
+        <v>0.1537494139357569</v>
       </c>
       <c r="C76">
-        <v>259.840758792445</v>
+        <v>255.6900034679808</v>
       </c>
       <c r="D76">
-        <v>604.550758792445</v>
+        <v>605.3150034679808</v>
       </c>
       <c r="E76">
-        <v>11.00999999999999</v>
+        <v>15.92500000000001</v>
       </c>
       <c r="F76">
-        <v>363.71</v>
+        <v>368.625</v>
       </c>
       <c r="G76">
         <v>19</v>
@@ -7519,28 +7519,28 @@
         <v>64.8</v>
       </c>
       <c r="M76">
-        <v>27.569218</v>
+        <v>27.941775</v>
       </c>
       <c r="N76">
-        <v>37.230782</v>
+        <v>36.85822499999999</v>
       </c>
       <c r="O76">
-        <v>8.37692595</v>
+        <v>8.293100624999997</v>
       </c>
       <c r="P76">
-        <v>28.85385605</v>
+        <v>28.56512437499999</v>
       </c>
       <c r="Q76">
-        <v>31.55385605</v>
+        <v>31.265124375</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4246714558262735</v>
+        <v>0.4387626557430275</v>
       </c>
       <c r="T76">
-        <v>2.641659461419617</v>
+        <v>2.739909543368037</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.350447517227366</v>
+        <v>2.319108216997667</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1537494139357569</v>
+        <v>0.1536129493566827</v>
       </c>
       <c r="C77">
-        <v>255.6900034679808</v>
+        <v>251.5411828337106</v>
       </c>
       <c r="D77">
-        <v>605.3150034679808</v>
+        <v>606.0811828337106</v>
       </c>
       <c r="E77">
-        <v>15.92500000000001</v>
+        <v>20.84000000000003</v>
       </c>
       <c r="F77">
-        <v>368.625</v>
+        <v>373.54</v>
       </c>
       <c r="G77">
         <v>19</v>
@@ -7601,28 +7601,28 @@
         <v>64.8</v>
       </c>
       <c r="M77">
-        <v>27.941775</v>
+        <v>28.314332</v>
       </c>
       <c r="N77">
-        <v>36.85822499999999</v>
+        <v>36.48566799999999</v>
       </c>
       <c r="O77">
-        <v>8.293100624999997</v>
+        <v>8.209275299999998</v>
       </c>
       <c r="P77">
-        <v>28.56512437499999</v>
+        <v>28.27639269999999</v>
       </c>
       <c r="Q77">
-        <v>31.265124375</v>
+        <v>30.97639269999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4387626557430275</v>
+        <v>0.4540281223195111</v>
       </c>
       <c r="T77">
-        <v>2.739909543368037</v>
+        <v>2.846347132145493</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.319108216997667</v>
+        <v>2.288593635195066</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1536129493566827</v>
+        <v>0.1534764847776084</v>
       </c>
       <c r="C78">
-        <v>251.5411828337106</v>
+        <v>247.394304245466</v>
       </c>
       <c r="D78">
-        <v>606.0811828337106</v>
+        <v>606.849304245466</v>
       </c>
       <c r="E78">
-        <v>20.84000000000003</v>
+        <v>25.755</v>
       </c>
       <c r="F78">
-        <v>373.54</v>
+        <v>378.455</v>
       </c>
       <c r="G78">
         <v>19</v>
@@ -7683,28 +7683,28 @@
         <v>64.8</v>
       </c>
       <c r="M78">
-        <v>28.314332</v>
+        <v>28.686889</v>
       </c>
       <c r="N78">
-        <v>36.48566799999999</v>
+        <v>36.113111</v>
       </c>
       <c r="O78">
-        <v>8.209275299999998</v>
+        <v>8.125449974999999</v>
       </c>
       <c r="P78">
-        <v>28.27639269999999</v>
+        <v>27.987661025</v>
       </c>
       <c r="Q78">
-        <v>30.97639269999999</v>
+        <v>30.687661025</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4540281223195111</v>
+        <v>0.4706210207722106</v>
       </c>
       <c r="T78">
-        <v>2.846347132145493</v>
+        <v>2.962040163425335</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.288593635195066</v>
+        <v>2.258871639932793</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1534764847776084</v>
+        <v>0.1533400201985342</v>
       </c>
       <c r="C79">
-        <v>247.394304245466</v>
+        <v>243.2493750964148</v>
       </c>
       <c r="D79">
-        <v>606.849304245466</v>
+        <v>607.6193750964148</v>
       </c>
       <c r="E79">
-        <v>25.755</v>
+        <v>30.67000000000002</v>
       </c>
       <c r="F79">
-        <v>378.455</v>
+        <v>383.37</v>
       </c>
       <c r="G79">
         <v>19</v>
@@ -7765,28 +7765,28 @@
         <v>64.8</v>
       </c>
       <c r="M79">
-        <v>28.686889</v>
+        <v>29.059446</v>
       </c>
       <c r="N79">
-        <v>36.113111</v>
+        <v>35.740554</v>
       </c>
       <c r="O79">
-        <v>8.125449974999999</v>
+        <v>8.041624649999999</v>
       </c>
       <c r="P79">
-        <v>27.987661025</v>
+        <v>27.69892935</v>
       </c>
       <c r="Q79">
-        <v>30.687661025</v>
+        <v>30.39892935</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4706210207722106</v>
+        <v>0.4887223645387918</v>
       </c>
       <c r="T79">
-        <v>2.962040163425335</v>
+        <v>3.088250743003345</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.258871639932793</v>
+        <v>2.229911747113142</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1533400201985342</v>
+        <v>0.15320355561946</v>
       </c>
       <c r="C80">
-        <v>243.2493750964148</v>
+        <v>239.1064028173001</v>
       </c>
       <c r="D80">
-        <v>607.6193750964148</v>
+        <v>608.3914028173001</v>
       </c>
       <c r="E80">
-        <v>30.67000000000002</v>
+        <v>35.58500000000004</v>
       </c>
       <c r="F80">
-        <v>383.37</v>
+        <v>388.285</v>
       </c>
       <c r="G80">
         <v>19</v>
@@ -7847,28 +7847,28 @@
         <v>64.8</v>
       </c>
       <c r="M80">
-        <v>29.059446</v>
+        <v>29.43200300000001</v>
       </c>
       <c r="N80">
-        <v>35.740554</v>
+        <v>35.36799699999999</v>
       </c>
       <c r="O80">
-        <v>8.041624649999999</v>
+        <v>7.957799324999997</v>
       </c>
       <c r="P80">
-        <v>27.69892935</v>
+        <v>27.41019767499999</v>
       </c>
       <c r="Q80">
-        <v>30.39892935</v>
+        <v>30.11019767499999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4887223645387918</v>
+        <v>0.5085476458069522</v>
       </c>
       <c r="T80">
-        <v>3.088250743003345</v>
+        <v>3.226481377779261</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.229911747113142</v>
+        <v>2.201685016137025</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.15320355561946</v>
+        <v>0.1530670910403857</v>
       </c>
       <c r="C81">
-        <v>239.1064028173001</v>
+        <v>234.9653948766781</v>
       </c>
       <c r="D81">
-        <v>608.3914028173001</v>
+        <v>609.1653948766782</v>
       </c>
       <c r="E81">
-        <v>35.58500000000004</v>
+        <v>40.50000000000006</v>
       </c>
       <c r="F81">
-        <v>388.285</v>
+        <v>393.2</v>
       </c>
       <c r="G81">
         <v>19</v>
@@ -7929,28 +7929,28 @@
         <v>64.8</v>
       </c>
       <c r="M81">
-        <v>29.43200300000001</v>
+        <v>29.80456000000001</v>
       </c>
       <c r="N81">
-        <v>35.36799699999999</v>
+        <v>34.99543999999999</v>
       </c>
       <c r="O81">
-        <v>7.957799324999997</v>
+        <v>7.873973999999998</v>
       </c>
       <c r="P81">
-        <v>27.41019767499999</v>
+        <v>27.12146599999999</v>
       </c>
       <c r="Q81">
-        <v>30.11019767499999</v>
+        <v>29.82146599999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5085476458069522</v>
+        <v>0.5303554552019288</v>
       </c>
       <c r="T81">
-        <v>3.226481377779261</v>
+        <v>3.378535076032769</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.201685016137025</v>
+        <v>2.174163953435313</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1530670910403857</v>
+        <v>0.1529306264613115</v>
       </c>
       <c r="C82">
-        <v>234.9653948766781</v>
+        <v>230.8263587811593</v>
       </c>
       <c r="D82">
-        <v>609.1653948766782</v>
+        <v>609.9413587811594</v>
       </c>
       <c r="E82">
-        <v>40.50000000000006</v>
+        <v>45.41500000000002</v>
       </c>
       <c r="F82">
-        <v>393.2</v>
+        <v>398.115</v>
       </c>
       <c r="G82">
         <v>19</v>
@@ -8011,28 +8011,28 @@
         <v>64.8</v>
       </c>
       <c r="M82">
-        <v>29.80456000000001</v>
+        <v>30.177117</v>
       </c>
       <c r="N82">
-        <v>34.99543999999999</v>
+        <v>34.62288299999999</v>
       </c>
       <c r="O82">
-        <v>7.873973999999998</v>
+        <v>7.790148674999999</v>
       </c>
       <c r="P82">
-        <v>27.12146599999999</v>
+        <v>26.832734325</v>
       </c>
       <c r="Q82">
-        <v>29.82146599999999</v>
+        <v>29.532734325</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5303554552019288</v>
+        <v>0.5544588234805869</v>
       </c>
       <c r="T82">
-        <v>3.378535076032769</v>
+        <v>3.546594426734013</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.174163953435313</v>
+        <v>2.147322423145988</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1529306264613115</v>
+        <v>0.1527941618822373</v>
       </c>
       <c r="C83">
-        <v>230.8263587811593</v>
+        <v>226.689302075651</v>
       </c>
       <c r="D83">
-        <v>609.9413587811594</v>
+        <v>610.7193020756511</v>
       </c>
       <c r="E83">
-        <v>45.41500000000002</v>
+        <v>50.33000000000004</v>
       </c>
       <c r="F83">
-        <v>398.115</v>
+        <v>403.03</v>
       </c>
       <c r="G83">
         <v>19</v>
@@ -8093,28 +8093,28 @@
         <v>64.8</v>
       </c>
       <c r="M83">
-        <v>30.177117</v>
+        <v>30.549674</v>
       </c>
       <c r="N83">
-        <v>34.62288299999999</v>
+        <v>34.25032599999999</v>
       </c>
       <c r="O83">
-        <v>7.790148674999999</v>
+        <v>7.706323349999999</v>
       </c>
       <c r="P83">
-        <v>26.832734325</v>
+        <v>26.54400265</v>
       </c>
       <c r="Q83">
-        <v>29.532734325</v>
+        <v>29.24400265</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5544588234805869</v>
+        <v>0.5812403437902072</v>
       </c>
       <c r="T83">
-        <v>3.546594426734013</v>
+        <v>3.733327038624286</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.147322423145988</v>
+        <v>2.121135564327135</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1527941618822373</v>
+        <v>0.152657697303163</v>
       </c>
       <c r="C84">
-        <v>226.689302075651</v>
+        <v>222.5542323436017</v>
       </c>
       <c r="D84">
-        <v>610.7193020756511</v>
+        <v>611.4992323436018</v>
       </c>
       <c r="E84">
-        <v>50.33000000000004</v>
+        <v>55.24500000000006</v>
       </c>
       <c r="F84">
-        <v>403.03</v>
+        <v>407.9450000000001</v>
       </c>
       <c r="G84">
         <v>19</v>
@@ -8175,28 +8175,28 @@
         <v>64.8</v>
       </c>
       <c r="M84">
-        <v>30.549674</v>
+        <v>30.92223100000001</v>
       </c>
       <c r="N84">
-        <v>34.25032599999999</v>
+        <v>33.87776899999999</v>
       </c>
       <c r="O84">
-        <v>7.706323349999999</v>
+        <v>7.622498024999997</v>
       </c>
       <c r="P84">
-        <v>26.54400265</v>
+        <v>26.25527097499999</v>
       </c>
       <c r="Q84">
-        <v>29.24400265</v>
+        <v>28.95527097499999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5812403437902072</v>
+        <v>0.6111726311950768</v>
       </c>
       <c r="T84">
-        <v>3.733327038624286</v>
+        <v>3.942028193089884</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.121135564327135</v>
+        <v>2.095579714154518</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.152657697303163</v>
+        <v>0.1525212327240888</v>
       </c>
       <c r="C85">
-        <v>222.5542323436017</v>
+        <v>218.4211572072484</v>
       </c>
       <c r="D85">
-        <v>611.4992323436018</v>
+        <v>612.2811572072484</v>
       </c>
       <c r="E85">
-        <v>55.24500000000006</v>
+        <v>60.16000000000003</v>
       </c>
       <c r="F85">
-        <v>407.9450000000001</v>
+        <v>412.86</v>
       </c>
       <c r="G85">
         <v>19</v>
@@ -8257,28 +8257,28 @@
         <v>64.8</v>
       </c>
       <c r="M85">
-        <v>30.92223100000001</v>
+        <v>31.294788</v>
       </c>
       <c r="N85">
-        <v>33.87776899999999</v>
+        <v>33.50521199999999</v>
       </c>
       <c r="O85">
-        <v>7.622498024999997</v>
+        <v>7.538672699999998</v>
       </c>
       <c r="P85">
-        <v>26.25527097499999</v>
+        <v>25.96653929999999</v>
       </c>
       <c r="Q85">
-        <v>28.95527097499999</v>
+        <v>28.6665393</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6111726311950768</v>
+        <v>0.6448464545255554</v>
       </c>
       <c r="T85">
-        <v>3.942028193089884</v>
+        <v>4.176816991863683</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.095579714154518</v>
+        <v>2.07063233660506</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1525212327240888</v>
+        <v>0.1523847681450146</v>
       </c>
       <c r="C86">
-        <v>218.4211572072484</v>
+        <v>214.2900843278637</v>
       </c>
       <c r="D86">
-        <v>612.2811572072484</v>
+        <v>613.0650843278637</v>
       </c>
       <c r="E86">
-        <v>60.15999999999997</v>
+        <v>65.07499999999999</v>
       </c>
       <c r="F86">
-        <v>412.86</v>
+        <v>417.775</v>
       </c>
       <c r="G86">
         <v>19</v>
@@ -8339,28 +8339,28 @@
         <v>64.8</v>
       </c>
       <c r="M86">
-        <v>31.294788</v>
+        <v>31.667345</v>
       </c>
       <c r="N86">
-        <v>33.505212</v>
+        <v>33.132655</v>
       </c>
       <c r="O86">
-        <v>7.5386727</v>
+        <v>7.454847375</v>
       </c>
       <c r="P86">
-        <v>25.9665393</v>
+        <v>25.677807625</v>
       </c>
       <c r="Q86">
-        <v>28.6665393</v>
+        <v>28.377807625</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.644846454525555</v>
+        <v>0.6830101209667637</v>
       </c>
       <c r="T86">
-        <v>4.176816991863681</v>
+        <v>4.442910963807318</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.07063233660506</v>
+        <v>2.046271956174412</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1523847681450146</v>
+        <v>0.1522483035659404</v>
       </c>
       <c r="C87">
-        <v>214.2900843278637</v>
+        <v>210.1610214060068</v>
       </c>
       <c r="D87">
-        <v>613.0650843278637</v>
+        <v>613.8510214060068</v>
       </c>
       <c r="E87">
-        <v>65.07499999999999</v>
+        <v>69.99000000000001</v>
       </c>
       <c r="F87">
-        <v>417.775</v>
+        <v>422.69</v>
       </c>
       <c r="G87">
         <v>19</v>
@@ -8421,28 +8421,28 @@
         <v>64.8</v>
       </c>
       <c r="M87">
-        <v>31.667345</v>
+        <v>32.039902</v>
       </c>
       <c r="N87">
-        <v>33.132655</v>
+        <v>32.76009799999999</v>
       </c>
       <c r="O87">
-        <v>7.454847375</v>
+        <v>7.371022049999999</v>
       </c>
       <c r="P87">
-        <v>25.677807625</v>
+        <v>25.38907594999999</v>
       </c>
       <c r="Q87">
-        <v>28.377807625</v>
+        <v>28.08907594999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6830101209667637</v>
+        <v>0.7266257397567167</v>
       </c>
       <c r="T87">
-        <v>4.442910963807318</v>
+        <v>4.747018360314333</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.046271956174412</v>
+        <v>2.022478096218896</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1522483035659404</v>
+        <v>0.1616861889868661</v>
       </c>
       <c r="C88">
-        <v>210.1610214060068</v>
+        <v>155.2533893572928</v>
       </c>
       <c r="D88">
-        <v>613.8510214060068</v>
+        <v>563.8583893572928</v>
       </c>
       <c r="E88">
-        <v>69.99000000000001</v>
+        <v>74.90500000000003</v>
       </c>
       <c r="F88">
-        <v>422.69</v>
+        <v>427.605</v>
       </c>
       <c r="G88">
         <v>19</v>
@@ -8503,45 +8503,45 @@
         <v>64.8</v>
       </c>
       <c r="M88">
-        <v>32.039902</v>
+        <v>38.48445</v>
       </c>
       <c r="N88">
-        <v>32.76009799999999</v>
+        <v>26.31554999999999</v>
       </c>
       <c r="O88">
-        <v>7.371022049999999</v>
+        <v>5.920998749999999</v>
       </c>
       <c r="P88">
-        <v>25.38907594999999</v>
+        <v>20.39455125</v>
       </c>
       <c r="Q88">
-        <v>28.08907594999999</v>
+        <v>23.09455125</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7266257397567167</v>
+        <v>0.776951453745124</v>
       </c>
       <c r="T88">
-        <v>4.747018360314333</v>
+        <v>5.097911510130118</v>
       </c>
       <c r="U88">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V88">
         <v>0.225</v>
       </c>
       <c r="W88">
-        <v>0.05874500000000001</v>
+        <v>0.06974999999999999</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y88">
-        <v>2.022478096218896</v>
+        <v>1.683796962149647</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1616861889868661</v>
+        <v>0.1616597744077919</v>
       </c>
       <c r="C89">
-        <v>155.2533893572928</v>
+        <v>150.4669420157843</v>
       </c>
       <c r="D89">
-        <v>563.8583893572928</v>
+        <v>563.9869420157843</v>
       </c>
       <c r="E89">
-        <v>74.90500000000003</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="F89">
-        <v>427.605</v>
+        <v>432.52</v>
       </c>
       <c r="G89">
         <v>19</v>
@@ -8585,28 +8585,28 @@
         <v>64.8</v>
       </c>
       <c r="M89">
-        <v>38.48445</v>
+        <v>38.9268</v>
       </c>
       <c r="N89">
-        <v>26.31554999999999</v>
+        <v>25.8732</v>
       </c>
       <c r="O89">
-        <v>5.920998749999999</v>
+        <v>5.82147</v>
       </c>
       <c r="P89">
-        <v>20.39455125</v>
+        <v>20.05173</v>
       </c>
       <c r="Q89">
-        <v>23.09455125</v>
+        <v>22.75173</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.776951453745124</v>
+        <v>0.8356647867315992</v>
       </c>
       <c r="T89">
-        <v>5.097911510130118</v>
+        <v>5.50728685158187</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.683796962149647</v>
+        <v>1.664662905761583</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1616597744077919</v>
+        <v>0.1616333598287177</v>
       </c>
       <c r="C90">
-        <v>150.4669420157843</v>
+        <v>145.6805533044384</v>
       </c>
       <c r="D90">
-        <v>563.9869420157843</v>
+        <v>564.1155533044384</v>
       </c>
       <c r="E90">
-        <v>79.81999999999999</v>
+        <v>84.73500000000001</v>
       </c>
       <c r="F90">
-        <v>432.52</v>
+        <v>437.435</v>
       </c>
       <c r="G90">
         <v>19</v>
@@ -8667,28 +8667,28 @@
         <v>64.8</v>
       </c>
       <c r="M90">
-        <v>38.9268</v>
+        <v>39.36915</v>
       </c>
       <c r="N90">
-        <v>25.8732</v>
+        <v>25.43085</v>
       </c>
       <c r="O90">
-        <v>5.82147</v>
+        <v>5.72194125</v>
       </c>
       <c r="P90">
-        <v>20.05173</v>
+        <v>19.70890875</v>
       </c>
       <c r="Q90">
-        <v>22.75173</v>
+        <v>22.40890875</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8356647867315992</v>
+        <v>0.9050532711701607</v>
       </c>
       <c r="T90">
-        <v>5.50728685158187</v>
+        <v>5.991094073297575</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.664662905761583</v>
+        <v>1.645958828168756</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1616333598287177</v>
+        <v>0.1616069452496434</v>
       </c>
       <c r="C91">
-        <v>145.6805533044384</v>
+        <v>140.8942232633743</v>
       </c>
       <c r="D91">
-        <v>564.1155533044384</v>
+        <v>564.2442232633744</v>
       </c>
       <c r="E91">
-        <v>84.73500000000001</v>
+        <v>89.65000000000003</v>
       </c>
       <c r="F91">
-        <v>437.435</v>
+        <v>442.35</v>
       </c>
       <c r="G91">
         <v>19</v>
@@ -8749,28 +8749,28 @@
         <v>64.8</v>
       </c>
       <c r="M91">
-        <v>39.36915</v>
+        <v>39.8115</v>
       </c>
       <c r="N91">
-        <v>25.43085</v>
+        <v>24.98849999999999</v>
       </c>
       <c r="O91">
-        <v>5.72194125</v>
+        <v>5.622412499999999</v>
       </c>
       <c r="P91">
-        <v>19.70890875</v>
+        <v>19.3660875</v>
       </c>
       <c r="Q91">
-        <v>22.40890875</v>
+        <v>22.0660875</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9050532711701607</v>
+        <v>0.9883194524964345</v>
       </c>
       <c r="T91">
-        <v>5.991094073297575</v>
+        <v>6.571662739356421</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.645958828168756</v>
+        <v>1.627670396744659</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1616069452496434</v>
+        <v>0.1615805306705692</v>
       </c>
       <c r="C92">
-        <v>140.8942232633743</v>
+        <v>136.1079519327477</v>
       </c>
       <c r="D92">
-        <v>564.2442232633744</v>
+        <v>564.3729519327477</v>
       </c>
       <c r="E92">
-        <v>89.65000000000003</v>
+        <v>94.56500000000005</v>
       </c>
       <c r="F92">
-        <v>442.35</v>
+        <v>447.265</v>
       </c>
       <c r="G92">
         <v>19</v>
@@ -8831,28 +8831,28 @@
         <v>64.8</v>
       </c>
       <c r="M92">
-        <v>39.8115</v>
+        <v>40.25385</v>
       </c>
       <c r="N92">
-        <v>24.98849999999999</v>
+        <v>24.54615</v>
       </c>
       <c r="O92">
-        <v>5.622412499999999</v>
+        <v>5.522883749999999</v>
       </c>
       <c r="P92">
-        <v>19.3660875</v>
+        <v>19.02326625</v>
       </c>
       <c r="Q92">
-        <v>22.0660875</v>
+        <v>21.72326625</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.9883194524964345</v>
+        <v>1.090089229672992</v>
       </c>
       <c r="T92">
-        <v>6.571662739356421</v>
+        <v>7.281246664539456</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.627670396744659</v>
+        <v>1.609783908868344</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1615805306705692</v>
+        <v>0.161554116091495</v>
       </c>
       <c r="C93">
-        <v>136.1079519327477</v>
+        <v>131.321739352751</v>
       </c>
       <c r="D93">
-        <v>564.3729519327477</v>
+        <v>564.501739352751</v>
       </c>
       <c r="E93">
-        <v>94.56500000000005</v>
+        <v>99.48000000000002</v>
       </c>
       <c r="F93">
-        <v>447.265</v>
+        <v>452.18</v>
       </c>
       <c r="G93">
         <v>19</v>
@@ -8913,28 +8913,28 @@
         <v>64.8</v>
       </c>
       <c r="M93">
-        <v>40.25385</v>
+        <v>40.6962</v>
       </c>
       <c r="N93">
-        <v>24.54615</v>
+        <v>24.1038</v>
       </c>
       <c r="O93">
-        <v>5.522883749999999</v>
+        <v>5.423355</v>
       </c>
       <c r="P93">
-        <v>19.02326625</v>
+        <v>18.680445</v>
       </c>
       <c r="Q93">
-        <v>21.72326625</v>
+        <v>21.380445</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.090089229672992</v>
+        <v>1.217301451143688</v>
       </c>
       <c r="T93">
-        <v>7.281246664539456</v>
+        <v>8.16822657101825</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.609783908868344</v>
+        <v>1.592286257684993</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.161554116091495</v>
+        <v>0.1615277015124207</v>
       </c>
       <c r="C94">
-        <v>131.321739352751</v>
+        <v>126.5355855636132</v>
       </c>
       <c r="D94">
-        <v>564.501739352751</v>
+        <v>564.6305855636132</v>
       </c>
       <c r="E94">
-        <v>99.48000000000002</v>
+        <v>104.395</v>
       </c>
       <c r="F94">
-        <v>452.18</v>
+        <v>457.095</v>
       </c>
       <c r="G94">
         <v>19</v>
@@ -8995,28 +8995,28 @@
         <v>64.8</v>
       </c>
       <c r="M94">
-        <v>40.6962</v>
+        <v>41.13855</v>
       </c>
       <c r="N94">
-        <v>24.1038</v>
+        <v>23.66144999999999</v>
       </c>
       <c r="O94">
-        <v>5.423355</v>
+        <v>5.323826249999999</v>
       </c>
       <c r="P94">
-        <v>18.680445</v>
+        <v>18.33762375</v>
       </c>
       <c r="Q94">
-        <v>21.380445</v>
+        <v>21.03762375</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.217301451143688</v>
+        <v>1.380860021606012</v>
       </c>
       <c r="T94">
-        <v>8.16822657101825</v>
+        <v>9.308629307919556</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.592286257684993</v>
+        <v>1.575164900075476</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1615277015124207</v>
+        <v>0.1615012869333465</v>
       </c>
       <c r="C95">
-        <v>126.5355855636132</v>
+        <v>121.7494906056002</v>
       </c>
       <c r="D95">
-        <v>564.6305855636132</v>
+        <v>564.7594906056003</v>
       </c>
       <c r="E95">
-        <v>104.395</v>
+        <v>109.3100000000001</v>
       </c>
       <c r="F95">
-        <v>457.095</v>
+        <v>462.01</v>
       </c>
       <c r="G95">
         <v>19</v>
@@ -9077,28 +9077,28 @@
         <v>64.8</v>
       </c>
       <c r="M95">
-        <v>41.13855</v>
+        <v>41.5809</v>
       </c>
       <c r="N95">
-        <v>23.66144999999999</v>
+        <v>23.2191</v>
       </c>
       <c r="O95">
-        <v>5.323826249999999</v>
+        <v>5.2242975</v>
       </c>
       <c r="P95">
-        <v>18.33762375</v>
+        <v>17.9948025</v>
       </c>
       <c r="Q95">
-        <v>21.03762375</v>
+        <v>20.6948025</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.380860021606012</v>
+        <v>1.598938115555777</v>
       </c>
       <c r="T95">
-        <v>9.308629307919556</v>
+        <v>10.82916629045463</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.575164900075476</v>
+        <v>1.558407826670418</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1615012869333465</v>
+        <v>0.1614748723542723</v>
       </c>
       <c r="C96">
-        <v>121.7494906056002</v>
+        <v>116.9634545190145</v>
       </c>
       <c r="D96">
-        <v>564.7594906056003</v>
+        <v>564.8884545190145</v>
       </c>
       <c r="E96">
-        <v>109.3100000000001</v>
+        <v>114.225</v>
       </c>
       <c r="F96">
-        <v>462.01</v>
+        <v>466.925</v>
       </c>
       <c r="G96">
         <v>19</v>
@@ -9159,28 +9159,28 @@
         <v>64.8</v>
       </c>
       <c r="M96">
-        <v>41.5809</v>
+        <v>42.02325</v>
       </c>
       <c r="N96">
-        <v>23.2191</v>
+        <v>22.77675</v>
       </c>
       <c r="O96">
-        <v>5.2242975</v>
+        <v>5.12476875</v>
       </c>
       <c r="P96">
-        <v>17.9948025</v>
+        <v>17.65198125</v>
       </c>
       <c r="Q96">
-        <v>20.6948025</v>
+        <v>20.35198125</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.598938115555777</v>
+        <v>1.904247447085448</v>
       </c>
       <c r="T96">
-        <v>10.82916629045463</v>
+        <v>12.95791806600374</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.558407826670418</v>
+        <v>1.542003533758098</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1614748723542723</v>
+        <v>0.1614484577751981</v>
       </c>
       <c r="C97">
-        <v>116.9634545190145</v>
+        <v>112.1774773441958</v>
       </c>
       <c r="D97">
-        <v>564.8884545190145</v>
+        <v>565.0174773441959</v>
       </c>
       <c r="E97">
-        <v>114.225</v>
+        <v>119.14</v>
       </c>
       <c r="F97">
-        <v>466.925</v>
+        <v>471.84</v>
       </c>
       <c r="G97">
         <v>19</v>
@@ -9241,28 +9241,28 @@
         <v>64.8</v>
       </c>
       <c r="M97">
-        <v>42.02325</v>
+        <v>42.4656</v>
       </c>
       <c r="N97">
-        <v>22.77675</v>
+        <v>22.3344</v>
       </c>
       <c r="O97">
-        <v>5.12476875</v>
+        <v>5.025239999999999</v>
       </c>
       <c r="P97">
-        <v>17.65198125</v>
+        <v>17.30915999999999</v>
       </c>
       <c r="Q97">
-        <v>20.35198125</v>
+        <v>20.00916</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.904247447085448</v>
+        <v>2.362211444379956</v>
       </c>
       <c r="T97">
-        <v>12.95791806600374</v>
+        <v>16.15104572932741</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.542003533758098</v>
+        <v>1.525940996948118</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1614484577751981</v>
+        <v>0.1614220431961239</v>
       </c>
       <c r="C98">
-        <v>112.1774773441959</v>
+        <v>107.3915591215201</v>
       </c>
       <c r="D98">
-        <v>565.0174773441959</v>
+        <v>565.1465591215201</v>
       </c>
       <c r="E98">
-        <v>119.14</v>
+        <v>124.055</v>
       </c>
       <c r="F98">
-        <v>471.84</v>
+        <v>476.755</v>
       </c>
       <c r="G98">
         <v>19</v>
@@ -9323,28 +9323,28 @@
         <v>64.8</v>
       </c>
       <c r="M98">
-        <v>42.46559999999999</v>
+        <v>42.90795</v>
       </c>
       <c r="N98">
-        <v>22.3344</v>
+        <v>21.89205</v>
       </c>
       <c r="O98">
-        <v>5.025240000000001</v>
+        <v>4.92571125</v>
       </c>
       <c r="P98">
-        <v>17.30916</v>
+        <v>16.96633875</v>
       </c>
       <c r="Q98">
-        <v>20.00916</v>
+        <v>19.66633875</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.36221144437995</v>
+        <v>3.125484773204125</v>
       </c>
       <c r="T98">
-        <v>16.15104572932736</v>
+        <v>21.47292516820011</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.525940996948118</v>
+        <v>1.510209646464117</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1614220431961239</v>
+        <v>0.2094181358010633</v>
       </c>
       <c r="C99">
-        <v>107.3915591215201</v>
+        <v>-63.30473678530626</v>
       </c>
       <c r="D99">
-        <v>565.1465591215201</v>
+        <v>399.3652632146938</v>
       </c>
       <c r="E99">
-        <v>124.055</v>
+        <v>128.97</v>
       </c>
       <c r="F99">
-        <v>476.755</v>
+        <v>481.67</v>
       </c>
       <c r="G99">
         <v>19</v>
@@ -9405,45 +9405,45 @@
         <v>64.8</v>
       </c>
       <c r="M99">
-        <v>42.90795</v>
+        <v>70.70915600000001</v>
       </c>
       <c r="N99">
-        <v>21.89205</v>
+        <v>-5.90915600000001</v>
       </c>
       <c r="O99">
-        <v>4.92571125</v>
+        <v>-1.329560100000002</v>
       </c>
       <c r="P99">
-        <v>16.96633875</v>
+        <v>-4.579595900000008</v>
       </c>
       <c r="Q99">
-        <v>19.66633875</v>
+        <v>-1.879595900000005</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.125484773204125</v>
+        <v>4.760921439086733</v>
       </c>
       <c r="T99">
-        <v>21.47292516820011</v>
+        <v>32.87591337315569</v>
       </c>
       <c r="U99">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.225</v>
+        <v>0.2061967759875397</v>
       </c>
       <c r="W99">
-        <v>0.06974999999999999</v>
+        <v>0.1165303132850292</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y99">
-        <v>1.510209646464117</v>
+        <v>0.9164301155001764</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2094181358010633</v>
+        <v>0.2104281358010633</v>
       </c>
       <c r="C100">
-        <v>-63.30473678530626</v>
+        <v>-70.66985816877536</v>
       </c>
       <c r="D100">
-        <v>399.3652632146938</v>
+        <v>396.9151418312246</v>
       </c>
       <c r="E100">
-        <v>128.97</v>
+        <v>133.885</v>
       </c>
       <c r="F100">
-        <v>481.67</v>
+        <v>486.585</v>
       </c>
       <c r="G100">
         <v>19</v>
@@ -9487,37 +9487,37 @@
         <v>64.8</v>
       </c>
       <c r="M100">
-        <v>70.70915600000001</v>
+        <v>71.430678</v>
       </c>
       <c r="N100">
-        <v>-5.90915600000001</v>
+        <v>-6.630678000000003</v>
       </c>
       <c r="O100">
-        <v>-1.329560100000002</v>
+        <v>-1.491902550000001</v>
       </c>
       <c r="P100">
-        <v>-4.579595900000008</v>
+        <v>-5.138775450000002</v>
       </c>
       <c r="Q100">
-        <v>-1.879595900000005</v>
+        <v>-2.43877545</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.760921439086733</v>
+        <v>9.476042878173466</v>
       </c>
       <c r="T100">
-        <v>32.87591337315569</v>
+        <v>65.75182674631138</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.2061967759875397</v>
+        <v>0.2041139802704938</v>
       </c>
       <c r="W100">
-        <v>0.1165303132850292</v>
+        <v>0.1168360676962915</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.9164301155001764</v>
+        <v>0.9071732456466394</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2104281358010633</v>
-      </c>
-      <c r="C101">
-        <v>-70.66985816877536</v>
-      </c>
-      <c r="D101">
-        <v>396.9151418312246</v>
-      </c>
-      <c r="E101">
-        <v>133.885</v>
-      </c>
-      <c r="F101">
-        <v>486.585</v>
-      </c>
-      <c r="G101">
-        <v>19</v>
-      </c>
-      <c r="H101">
-        <v>138.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>67.5</v>
-      </c>
-      <c r="K101">
-        <v>2.700000000000003</v>
-      </c>
-      <c r="L101">
-        <v>64.8</v>
-      </c>
-      <c r="M101">
-        <v>71.430678</v>
-      </c>
-      <c r="N101">
-        <v>-6.630678000000003</v>
-      </c>
-      <c r="O101">
-        <v>-1.491902550000001</v>
-      </c>
-      <c r="P101">
-        <v>-5.138775450000002</v>
-      </c>
-      <c r="Q101">
-        <v>-2.43877545</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.476042878173466</v>
-      </c>
-      <c r="T101">
-        <v>65.75182674631138</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2041139802704938</v>
-      </c>
-      <c r="W101">
-        <v>0.1168360676962915</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.9071732456466394</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
